--- a/Smart-Order-API-document.xlsx
+++ b/Smart-Order-API-document.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\workspace\smart-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C08F6E1-5546-4E50-8349-6ADA2068F612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E8A60E-C13B-4BEA-B328-6AF628C424B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="687" activeTab="3" xr2:uid="{189FE3B2-D7F9-4DC5-8D24-13A8FA728144}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="687" firstSheet="3" activeTab="10" xr2:uid="{189FE3B2-D7F9-4DC5-8D24-13A8FA728144}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="2" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="512">
   <si>
     <t>Version</t>
   </si>
@@ -484,9 +484,6 @@
   </si>
   <si>
     <t>postSignIn</t>
-  </si>
-  <si>
-    <t>/api/v1/sign-in</t>
   </si>
   <si>
     <t>postSignUp</t>
@@ -2088,20 +2085,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Step2-2:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Create Access Token and Refresh Token</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">    "errorCode": "E00021",</t>
   </si>
   <si>
@@ -3347,9 +3330,6 @@
     <t>Unauthorized Refresh Token!</t>
   </si>
   <si>
-    <t>- Update Errors, Common, postSignUp, postRefreshToken and postToken Sheet.</t>
-  </si>
-  <si>
     <t>- Errors.
 - APIs.
 - Common.
@@ -3367,11 +3347,42 @@
 - postUserDetail</t>
   </si>
   <si>
+    <t xml:space="preserve">    "message": "The ${fieldName} has an error regarding its ${errorName}."</t>
+  </si>
+  <si>
+    <r>
+      <t>Step3:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Create Access Token and Refresh Token</t>
+    </r>
+  </si>
+  <si>
+    <t>AND USER_DELETE_FLG = 0</t>
+  </si>
+  <si>
+    <t>E00035</t>
+  </si>
+  <si>
+    <t>E00036</t>
+  </si>
+  <si>
     <t>- Errors.
 - Common.
 - postToken.
 - postRefreshToken.
-- postSignUp.</t>
+- postSignUp.
+-postSignIn</t>
+  </si>
+  <si>
+    <t>- Update Errors, Common, postSignIn, postSignUp, postRefreshToken and postToken Sheet.</t>
   </si>
 </sst>
 </file>
@@ -3897,7 +3908,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4310,6 +4321,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -5261,7 +5282,7 @@
       </c>
       <c r="D8" s="67"/>
       <c r="E8" s="68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F8" s="69"/>
       <c r="G8" s="69"/>
@@ -5272,7 +5293,7 @@
       <c r="L8" s="69"/>
       <c r="M8" s="69"/>
       <c r="N8" s="70" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O8" s="75"/>
       <c r="P8" s="72">
@@ -5286,7 +5307,7 @@
       </c>
       <c r="D9" s="67"/>
       <c r="E9" s="68" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F9" s="69"/>
       <c r="G9" s="69"/>
@@ -5297,7 +5318,7 @@
       <c r="L9" s="69"/>
       <c r="M9" s="69"/>
       <c r="N9" s="76" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="O9" s="77"/>
       <c r="P9" s="72">
@@ -5311,7 +5332,7 @@
       </c>
       <c r="D10" s="67"/>
       <c r="E10" s="68" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F10" s="69"/>
       <c r="G10" s="69"/>
@@ -5322,7 +5343,7 @@
       <c r="L10" s="69"/>
       <c r="M10" s="69"/>
       <c r="N10" s="70" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="O10" s="71"/>
       <c r="P10" s="72">
@@ -5330,13 +5351,13 @@
       </c>
       <c r="Q10" s="73"/>
     </row>
-    <row r="11" spans="3:21" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:21" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="67" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="67"/>
       <c r="E11" s="74" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F11" s="69"/>
       <c r="G11" s="69"/>
@@ -5347,7 +5368,7 @@
       <c r="L11" s="69"/>
       <c r="M11" s="69"/>
       <c r="N11" s="70" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O11" s="71"/>
       <c r="P11" s="72">
@@ -5920,7 +5941,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -5964,7 +5985,7 @@
       </c>
       <c r="C7" s="159"/>
       <c r="D7" s="83" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -5980,7 +6001,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -6012,7 +6033,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -6028,7 +6049,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -6044,7 +6065,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="161" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E12" s="160"/>
       <c r="F12" s="160"/>
@@ -6056,43 +6077,43 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
@@ -6111,19 +6132,19 @@
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G28" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L28" s="7"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G29" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G30" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -6137,25 +6158,25 @@
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E34" s="49" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F34"/>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E35"/>
       <c r="F35" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.25">
@@ -6163,7 +6184,7 @@
     </row>
     <row r="38" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E38" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
@@ -6182,19 +6203,19 @@
     </row>
     <row r="41" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F41" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K41" s="7"/>
     </row>
     <row r="42" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F42" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F43" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K43" s="7"/>
     </row>
@@ -6208,17 +6229,17 @@
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E49" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F49" s="156"/>
       <c r="G49" s="4"/>
@@ -6231,7 +6252,7 @@
     <row r="50" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E50" s="6"/>
       <c r="F50" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G50" s="24"/>
       <c r="L50" s="7"/>
@@ -6239,49 +6260,49 @@
     <row r="51" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E51" s="6"/>
       <c r="G51" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L51" s="7"/>
     </row>
     <row r="52" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E52" s="6"/>
       <c r="G52" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L52" s="7"/>
     </row>
     <row r="53" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E53" s="6"/>
       <c r="G53" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L53" s="7"/>
     </row>
     <row r="54" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E54" s="6"/>
       <c r="G54" s="24" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E55" s="6"/>
       <c r="G55" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E56" s="6"/>
       <c r="G56" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E57" s="6"/>
       <c r="F57" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G57" s="24"/>
       <c r="L57" s="7"/>
@@ -6289,14 +6310,14 @@
     <row r="58" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E58" s="6"/>
       <c r="G58" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E59" s="6"/>
       <c r="F59" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G59" s="24"/>
       <c r="L59" s="7"/>
@@ -6304,7 +6325,7 @@
     <row r="60" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E60" s="6"/>
       <c r="G60" s="24" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L60" s="7"/>
     </row>
@@ -6320,7 +6341,7 @@
     </row>
     <row r="63" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E63" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="5:12" x14ac:dyDescent="0.25">
@@ -6338,19 +6359,19 @@
     </row>
     <row r="66" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F66" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J66" s="7"/>
     </row>
     <row r="67" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F67" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J67" s="7"/>
     </row>
     <row r="68" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F68" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J68" s="7"/>
     </row>
@@ -6363,7 +6384,7 @@
     </row>
     <row r="71" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E71" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" spans="5:10" x14ac:dyDescent="0.25">
@@ -6384,7 +6405,7 @@
     </row>
     <row r="74" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F74" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G74" s="39"/>
       <c r="H74" s="39"/>
@@ -6393,7 +6414,7 @@
     </row>
     <row r="75" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F75" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G75" s="39"/>
       <c r="H75" s="39"/>
@@ -6402,7 +6423,7 @@
     </row>
     <row r="76" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F76" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G76" s="39"/>
       <c r="H76" s="39"/>
@@ -6418,7 +6439,7 @@
     </row>
     <row r="79" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E79" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="81" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -6455,77 +6476,77 @@
     <row r="86" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K86" s="7"/>
     </row>
     <row r="87" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K87" s="7"/>
     </row>
     <row r="88" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K88" s="7"/>
     </row>
     <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K89" s="7"/>
     </row>
     <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K90" s="7"/>
     </row>
     <row r="91" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K91" s="7"/>
     </row>
     <row r="92" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K92" s="7"/>
     </row>
     <row r="93" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K93" s="7"/>
     </row>
     <row r="94" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K94" s="7"/>
     </row>
     <row r="95" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K95" s="7"/>
     </row>
     <row r="96" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K96" s="7"/>
     </row>
@@ -6586,7 +6607,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -6630,7 +6651,7 @@
       </c>
       <c r="C7" s="159"/>
       <c r="D7" s="83" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -6646,7 +6667,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -6678,7 +6699,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -6694,7 +6715,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -6710,7 +6731,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="160" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E12" s="160"/>
       <c r="F12" s="160"/>
@@ -6722,43 +6743,43 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
@@ -6777,19 +6798,19 @@
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G28" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L28" s="7"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G29" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G30" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -6803,89 +6824,89 @@
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E34" s="49" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F34"/>
     </row>
     <row r="35" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E35"/>
       <c r="F35" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E37" s="49" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F37"/>
     </row>
     <row r="38" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E38"/>
       <c r="F38" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E39"/>
       <c r="F39" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E40" s="49" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F40"/>
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E41"/>
       <c r="F41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E42" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E43" s="49"/>
       <c r="F43" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E44" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E45" s="3"/>
       <c r="F45" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E46" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E47" s="3"/>
       <c r="F47" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="4:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6914,7 @@
     </row>
     <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E49" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="3:12" x14ac:dyDescent="0.25">
@@ -6912,19 +6933,19 @@
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F52" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K52" s="7"/>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F53" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K53" s="7"/>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F54" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K54" s="7"/>
     </row>
@@ -6938,17 +6959,17 @@
     </row>
     <row r="58" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D59" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E60" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F60" s="156"/>
       <c r="G60" s="4"/>
@@ -6961,7 +6982,7 @@
     <row r="61" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E61" s="6"/>
       <c r="F61" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G61" s="24"/>
       <c r="L61" s="7"/>
@@ -6969,49 +6990,49 @@
     <row r="62" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E62" s="6"/>
       <c r="G62" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L62" s="7"/>
     </row>
     <row r="63" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E63" s="6"/>
       <c r="G63" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L63" s="7"/>
     </row>
     <row r="64" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E64" s="6"/>
       <c r="G64" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L64" s="7"/>
     </row>
     <row r="65" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E65" s="6"/>
       <c r="G65" s="24" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L65" s="7"/>
     </row>
     <row r="66" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E66" s="6"/>
       <c r="G66" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L66" s="7"/>
     </row>
     <row r="67" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E67" s="6"/>
       <c r="G67" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L67" s="7"/>
     </row>
     <row r="68" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E68" s="6"/>
       <c r="F68" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G68" s="24"/>
       <c r="L68" s="7"/>
@@ -7019,14 +7040,14 @@
     <row r="69" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E69" s="6"/>
       <c r="G69" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L69" s="7"/>
     </row>
     <row r="70" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E70" s="6"/>
       <c r="F70" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G70" s="24"/>
       <c r="L70" s="7"/>
@@ -7034,14 +7055,14 @@
     <row r="71" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E71" s="6"/>
       <c r="G71" s="24" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L71" s="7"/>
     </row>
     <row r="72" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E72" s="50"/>
       <c r="F72" s="24" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J72" s="51"/>
       <c r="K72" s="51"/>
@@ -7050,17 +7071,17 @@
     <row r="73" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E73" s="50"/>
       <c r="F73" s="24" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L73" s="7"/>
     </row>
     <row r="74" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E74" s="50"/>
       <c r="F74" s="24" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J74" s="51"/>
       <c r="K74" s="51"/>
@@ -7069,7 +7090,7 @@
     <row r="75" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="25"/>
       <c r="F75" s="53" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10"/>
@@ -7080,7 +7101,7 @@
     </row>
     <row r="77" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E77" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="5:12" x14ac:dyDescent="0.25">
@@ -7098,19 +7119,19 @@
     </row>
     <row r="80" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F80" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J80" s="7"/>
     </row>
     <row r="81" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F81" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J81" s="7"/>
     </row>
     <row r="82" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F82" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J82" s="7"/>
     </row>
@@ -7123,7 +7144,7 @@
     </row>
     <row r="85" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E85" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="4:11" x14ac:dyDescent="0.25">
@@ -7141,19 +7162,19 @@
     </row>
     <row r="88" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F88" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J88" s="7"/>
     </row>
     <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F89" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J89" s="7"/>
     </row>
     <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F90" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J90" s="7"/>
     </row>
@@ -7166,7 +7187,7 @@
     </row>
     <row r="93" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E93" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="95" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7203,98 +7224,98 @@
     <row r="100" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K100" s="7"/>
     </row>
     <row r="101" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K101" s="7"/>
     </row>
     <row r="102" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K102" s="7"/>
     </row>
     <row r="103" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K103" s="7"/>
     </row>
     <row r="104" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K104" s="7"/>
     </row>
     <row r="105" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K105" s="7"/>
     </row>
     <row r="106" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K106" s="7"/>
     </row>
     <row r="107" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K107" s="7"/>
     </row>
     <row r="108" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="K108" s="7"/>
     </row>
     <row r="109" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K109" s="7"/>
     </row>
     <row r="110" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K110" s="7"/>
     </row>
     <row r="111" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K111" s="7"/>
     </row>
     <row r="112" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K112" s="7"/>
     </row>
     <row r="113" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K113" s="7"/>
     </row>
@@ -7344,9 +7365,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C783ED-428E-4204-9352-B01B1CB21AE2}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="B2:S125"/>
+  <dimension ref="B2:S118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="1"/>
@@ -7355,7 +7376,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -7415,7 +7436,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>143</v>
+        <v>492</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -7447,7 +7468,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -7463,7 +7484,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -7479,7 +7500,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="83" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E12" s="83"/>
       <c r="F12" s="83"/>
@@ -7491,31 +7512,31 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="18" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F18" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="4:12" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G19" s="153" t="s">
         <v>75</v>
       </c>
@@ -7525,29 +7546,29 @@
       <c r="K19" s="4"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G20" s="6"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G21" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G22" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G23" s="6" t="s">
-        <v>163</v>
+        <v>484</v>
       </c>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="9"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -7555,32 +7576,32 @@
       <c r="K24" s="10"/>
       <c r="L24" s="11"/>
     </row>
-    <row r="26" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27" spans="4:12" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E27" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="28" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F28" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F29" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="30" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F30" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="31" spans="4:12" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G31" s="153" t="s">
         <v>75</v>
       </c>
@@ -7588,51 +7609,79 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G32" s="6"/>
-      <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="H32" s="162"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="162"/>
+      <c r="K32" s="162"/>
+      <c r="L32" s="162"/>
+      <c r="M32" s="162"/>
+      <c r="N32" s="7"/>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.25">
       <c r="G33" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="L33" s="7"/>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="162"/>
+      <c r="K33" s="162"/>
+      <c r="L33" s="162"/>
+      <c r="M33" s="162"/>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="G34" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="L34" s="7"/>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="162"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="G35" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="162"/>
+      <c r="K35" s="162"/>
+      <c r="L35" s="162"/>
+      <c r="M35" s="162"/>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="40" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D40" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E41" s="155" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E41" s="155" t="s">
-        <v>176</v>
       </c>
       <c r="F41" s="156"/>
       <c r="G41" s="4"/>
@@ -7642,609 +7691,572 @@
       <c r="K41" s="4"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E42" s="6"/>
       <c r="F42" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G42" s="24"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E43" s="6"/>
       <c r="G43" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E44" s="6"/>
       <c r="G44" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E45" s="6"/>
       <c r="G45" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E46" s="6"/>
       <c r="G46" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E47" s="6"/>
       <c r="G47" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E48" s="6"/>
       <c r="G48" s="24" t="s">
-        <v>179</v>
+        <v>475</v>
       </c>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E49" s="6"/>
       <c r="F49" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G49" s="24"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E50" s="6"/>
       <c r="G50" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E51" s="6"/>
       <c r="F51" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G51" s="24"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E52" s="6"/>
       <c r="G52" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E53" s="6"/>
       <c r="G53" s="24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E54" s="25"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="11"/>
-    </row>
-    <row r="56" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="1" t="s">
+    <row r="54" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E54" s="6"/>
+      <c r="G54" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="L54" s="7"/>
+    </row>
+    <row r="55" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E55" s="25"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="11"/>
+    </row>
+    <row r="57" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="F58" s="153" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" s="154"/>
+      <c r="H58" s="164"/>
+      <c r="I58" s="164"/>
+      <c r="J58" s="164"/>
+      <c r="K58" s="164"/>
+      <c r="L58" s="164"/>
+      <c r="M58" s="165"/>
+    </row>
+    <row r="59" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="F59" s="170"/>
+      <c r="G59" s="166"/>
+      <c r="H59" s="166"/>
+      <c r="I59" s="166"/>
+      <c r="J59" s="166"/>
+      <c r="K59" s="166"/>
+      <c r="L59" s="166"/>
+      <c r="M59" s="167"/>
+    </row>
+    <row r="60" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="F60" s="170" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F57" s="153" t="s">
+      <c r="G60" s="166"/>
+      <c r="H60" s="166"/>
+      <c r="I60" s="166"/>
+      <c r="J60" s="166"/>
+      <c r="K60" s="166"/>
+      <c r="L60" s="166"/>
+      <c r="M60" s="167"/>
+    </row>
+    <row r="61" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="F61" s="170" t="s">
+        <v>343</v>
+      </c>
+      <c r="G61" s="166"/>
+      <c r="H61" s="166"/>
+      <c r="I61" s="166"/>
+      <c r="J61" s="166"/>
+      <c r="K61" s="166"/>
+      <c r="L61" s="166"/>
+      <c r="M61" s="167"/>
+    </row>
+    <row r="62" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="F62" s="170" t="s">
+        <v>486</v>
+      </c>
+      <c r="G62" s="166"/>
+      <c r="H62" s="166"/>
+      <c r="I62" s="166"/>
+      <c r="J62" s="166"/>
+      <c r="K62" s="166"/>
+      <c r="L62" s="166"/>
+      <c r="M62" s="167"/>
+    </row>
+    <row r="63" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F63" s="171"/>
+      <c r="G63" s="168"/>
+      <c r="H63" s="168"/>
+      <c r="I63" s="168"/>
+      <c r="J63" s="168"/>
+      <c r="K63" s="168"/>
+      <c r="L63" s="168"/>
+      <c r="M63" s="169"/>
+    </row>
+    <row r="65" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="66" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E66" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G57" s="154"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="38"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F58" s="43"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="40"/>
-    </row>
-    <row r="59" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F59" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="40"/>
-    </row>
-    <row r="60" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F60" s="43" t="s">
-        <v>242</v>
-      </c>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="40"/>
-    </row>
-    <row r="61" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F61" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="40"/>
-    </row>
-    <row r="62" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F62" s="44"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="42"/>
-    </row>
-    <row r="64" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D64" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="65" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E65" s="153" t="s">
+      <c r="F66" s="154"/>
+      <c r="G66" s="164"/>
+      <c r="H66" s="164"/>
+      <c r="I66" s="165"/>
+    </row>
+    <row r="67" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E67" s="170"/>
+      <c r="F67" s="166"/>
+      <c r="G67" s="166"/>
+      <c r="H67" s="166"/>
+      <c r="I67" s="167"/>
+    </row>
+    <row r="68" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E68" s="170" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68" s="166"/>
+      <c r="G68" s="166"/>
+      <c r="H68" s="166"/>
+      <c r="I68" s="167"/>
+    </row>
+    <row r="69" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E69" s="170" t="s">
+        <v>367</v>
+      </c>
+      <c r="F69" s="166"/>
+      <c r="G69" s="166"/>
+      <c r="H69" s="166"/>
+      <c r="I69" s="167"/>
+    </row>
+    <row r="70" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E70" s="170" t="s">
+        <v>231</v>
+      </c>
+      <c r="F70" s="166"/>
+      <c r="G70" s="166"/>
+      <c r="H70" s="166"/>
+      <c r="I70" s="167"/>
+    </row>
+    <row r="71" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E71" s="171"/>
+      <c r="F71" s="168"/>
+      <c r="G71" s="168"/>
+      <c r="H71" s="168"/>
+      <c r="I71" s="169"/>
+    </row>
+    <row r="74" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D74" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="76" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C76" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="77" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D77" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E78" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="F65" s="154"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="38"/>
-    </row>
-    <row r="66" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E66" s="43"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="40"/>
-    </row>
-    <row r="67" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E67" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="40"/>
-    </row>
-    <row r="68" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E68" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="40"/>
-    </row>
-    <row r="69" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E69" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="40"/>
-    </row>
-    <row r="70" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="44"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="42"/>
-    </row>
-    <row r="72" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E73" s="153" t="s">
+      <c r="F78" s="154"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+      <c r="K78" s="29"/>
+    </row>
+    <row r="79" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E79" s="34"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="31"/>
+    </row>
+    <row r="80" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E80" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="31"/>
+    </row>
+    <row r="81" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E81" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="31"/>
+    </row>
+    <row r="82" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E82" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="31"/>
+    </row>
+    <row r="83" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="35"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="33"/>
+    </row>
+    <row r="85" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D85" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E86" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="F73" s="154"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="38"/>
-    </row>
-    <row r="74" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E74" s="43"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
-      <c r="J74" s="40"/>
-    </row>
-    <row r="75" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E75" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="40"/>
-    </row>
-    <row r="76" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E76" s="43" t="s">
-        <v>255</v>
-      </c>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="40"/>
-    </row>
-    <row r="77" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E77" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="40"/>
-    </row>
-    <row r="78" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E78" s="44"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41"/>
-      <c r="J78" s="42"/>
-    </row>
-    <row r="80" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D80" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="82" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D82" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="84" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="85" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F85" s="153" t="s">
-        <v>75</v>
-      </c>
-      <c r="G85" s="154"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="28"/>
-      <c r="J85" s="28"/>
-      <c r="K85" s="28"/>
-      <c r="L85" s="29"/>
-    </row>
-    <row r="86" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F86" s="34"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="30"/>
-      <c r="J86" s="30"/>
-      <c r="K86" s="30"/>
-      <c r="L86" s="31"/>
-    </row>
-    <row r="87" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F87" s="34" t="s">
-        <v>162</v>
-      </c>
+      <c r="F86" s="154"/>
+      <c r="G86" s="28"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="28"/>
+      <c r="J86" s="28"/>
+      <c r="K86" s="29"/>
+    </row>
+    <row r="87" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E87" s="34"/>
+      <c r="F87" s="30"/>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
       <c r="I87" s="30"/>
       <c r="J87" s="30"/>
-      <c r="K87" s="30"/>
-      <c r="L87" s="31"/>
-    </row>
-    <row r="88" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F88" s="34" t="s">
-        <v>169</v>
-      </c>
+      <c r="K87" s="31"/>
+    </row>
+    <row r="88" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E88" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="F88" s="30"/>
       <c r="G88" s="30"/>
       <c r="H88" s="30"/>
       <c r="I88" s="30"/>
       <c r="J88" s="30"/>
-      <c r="K88" s="30"/>
-      <c r="L88" s="31"/>
-    </row>
-    <row r="89" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F89" s="34" t="s">
-        <v>170</v>
-      </c>
+      <c r="K88" s="31"/>
+    </row>
+    <row r="89" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E89" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="F89" s="30"/>
       <c r="G89" s="30"/>
       <c r="H89" s="30"/>
       <c r="I89" s="30"/>
       <c r="J89" s="30"/>
-      <c r="K89" s="30"/>
-      <c r="L89" s="31"/>
-    </row>
-    <row r="90" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F90" s="35"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="32"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="32"/>
-      <c r="L90" s="33"/>
-    </row>
-    <row r="92" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E92" s="1" t="s">
+      <c r="K89" s="31"/>
+    </row>
+    <row r="90" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E90" s="34" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="93" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F93" s="153" t="s">
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
+      <c r="K90" s="31"/>
+    </row>
+    <row r="91" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E91" s="35"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
+      <c r="K91" s="33"/>
+    </row>
+    <row r="93" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E94" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G93" s="154"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="28"/>
-      <c r="J93" s="28"/>
-      <c r="K93" s="28"/>
-      <c r="L93" s="29"/>
-    </row>
-    <row r="94" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F94" s="34"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="30"/>
-      <c r="J94" s="30"/>
-      <c r="K94" s="30"/>
-      <c r="L94" s="31"/>
-    </row>
-    <row r="95" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F95" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="30"/>
-      <c r="J95" s="30"/>
-      <c r="K95" s="30"/>
-      <c r="L95" s="31"/>
-    </row>
-    <row r="96" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F96" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="30"/>
-      <c r="J96" s="30"/>
-      <c r="K96" s="30"/>
-      <c r="L96" s="31"/>
-    </row>
-    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F97" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="30"/>
-      <c r="J97" s="30"/>
-      <c r="K97" s="30"/>
-      <c r="L97" s="31"/>
-    </row>
-    <row r="98" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F98" s="35"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
-      <c r="I98" s="32"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="32"/>
-      <c r="L98" s="33"/>
-    </row>
-    <row r="100" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E100" s="1" t="s">
+      <c r="F94" s="154"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
+      <c r="J94" s="28"/>
+      <c r="K94" s="29"/>
+    </row>
+    <row r="95" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E95" s="34"/>
+      <c r="F95" s="163"/>
+      <c r="G95" s="163"/>
+      <c r="H95" s="163"/>
+      <c r="I95" s="163"/>
+      <c r="J95" s="163"/>
+      <c r="K95" s="31"/>
+    </row>
+    <row r="96" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E96" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="F96" s="163"/>
+      <c r="G96" s="163"/>
+      <c r="H96" s="163"/>
+      <c r="I96" s="163"/>
+      <c r="J96" s="163"/>
+      <c r="K96" s="31"/>
+    </row>
+    <row r="97" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E97" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" s="163"/>
+      <c r="G97" s="163"/>
+      <c r="H97" s="163"/>
+      <c r="I97" s="163"/>
+      <c r="J97" s="163"/>
+      <c r="K97" s="31"/>
+    </row>
+    <row r="98" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E98" s="34" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="101" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F101" s="153" t="s">
-        <v>75</v>
-      </c>
-      <c r="G101" s="154"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="28"/>
-      <c r="J101" s="28"/>
-      <c r="K101" s="28"/>
-      <c r="L101" s="28"/>
-    </row>
-    <row r="102" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F102" s="34"/>
-      <c r="G102" s="30"/>
-      <c r="H102" s="30"/>
-      <c r="I102" s="30"/>
-      <c r="J102" s="30"/>
-      <c r="K102" s="30"/>
-      <c r="L102" s="30"/>
-    </row>
-    <row r="103" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F103" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="30"/>
-      <c r="J103" s="30"/>
-      <c r="K103" s="30"/>
-      <c r="L103" s="30"/>
-    </row>
-    <row r="104" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F104" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="30"/>
-      <c r="J104" s="30"/>
-      <c r="K104" s="30"/>
-      <c r="L104" s="30"/>
-    </row>
-    <row r="105" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F105" s="34" t="s">
+      <c r="F98" s="163"/>
+      <c r="G98" s="163"/>
+      <c r="H98" s="163"/>
+      <c r="I98" s="163"/>
+      <c r="J98" s="163"/>
+      <c r="K98" s="31"/>
+    </row>
+    <row r="99" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="35"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="32"/>
+      <c r="J99" s="32"/>
+      <c r="K99" s="33"/>
+    </row>
+    <row r="101" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D101" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="30"/>
-      <c r="J105" s="30"/>
-      <c r="K105" s="30"/>
-      <c r="L105" s="30"/>
-    </row>
-    <row r="106" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F106" s="35"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="32"/>
-      <c r="I106" s="32"/>
-      <c r="J106" s="32"/>
-      <c r="K106" s="32"/>
-      <c r="L106" s="32"/>
-    </row>
-    <row r="108" spans="4:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D102" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D105" s="157" t="s">
+        <v>111</v>
+      </c>
+      <c r="E105" s="158"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="5"/>
+    </row>
+    <row r="106" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D106" s="6"/>
+      <c r="J106" s="7"/>
+    </row>
+    <row r="107" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D107" s="6"/>
+      <c r="E107" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J107" s="7"/>
+    </row>
+    <row r="108" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D108" s="6"/>
       <c r="E108" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="109" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="E109" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="111" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D112" s="157" t="s">
-        <v>111</v>
-      </c>
-      <c r="E112" s="158"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="J108" s="7"/>
+    </row>
+    <row r="109" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D109" s="6"/>
+      <c r="E109" s="36" t="s">
+        <v>382</v>
+      </c>
+      <c r="J109" s="7"/>
+    </row>
+    <row r="110" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D110" s="6"/>
+      <c r="E110" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="J110" s="7"/>
+    </row>
+    <row r="111" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D111" s="6"/>
+      <c r="E111" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J111" s="7"/>
+    </row>
+    <row r="112" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D112" s="6"/>
+      <c r="E112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J112" s="7"/>
     </row>
     <row r="113" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
+      <c r="E113" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="J113" s="7"/>
     </row>
     <row r="114" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1" t="s">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="J114" s="7"/>
     </row>
     <row r="115" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="1" t="s">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="J115" s="7"/>
     </row>
     <row r="116" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
-      <c r="E116" s="36" t="s">
-        <v>384</v>
+      <c r="E116" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="J116" s="7"/>
     </row>
     <row r="117" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
-      <c r="E117" s="36" t="s">
-        <v>249</v>
+      <c r="E117" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D118" s="6"/>
-      <c r="E118" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="J118" s="7"/>
-    </row>
-    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D119" s="6"/>
-      <c r="E119" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J119" s="7"/>
-    </row>
-    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D120" s="6"/>
-      <c r="E120" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J120" s="7"/>
-    </row>
-    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D121" s="6"/>
-      <c r="E121" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J121" s="7"/>
-    </row>
-    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D122" s="6"/>
-      <c r="E122" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J122" s="7"/>
-    </row>
-    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D123" s="6"/>
-      <c r="E123" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="J123" s="7"/>
-    </row>
-    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D124" s="6"/>
-      <c r="E124" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J124" s="7"/>
-    </row>
-    <row r="125" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D125" s="9"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="10"/>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10"/>
-      <c r="I125" s="10"/>
-      <c r="J125" s="11"/>
+    <row r="118" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D118" s="9"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="10"/>
+      <c r="G118" s="10"/>
+      <c r="H118" s="10"/>
+      <c r="I118" s="10"/>
+      <c r="J118" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="D112:E112"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="F57:G57"/>
+  <mergeCells count="22">
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E94:F94"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="F85:G85"/>
     <mergeCell ref="E41:F41"/>
     <mergeCell ref="G31:H31"/>
+    <mergeCell ref="F58:G58"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:K10"/>
     <mergeCell ref="B11:C11"/>
@@ -8260,13 +8272,14 @@
     <mergeCell ref="D8:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8052CD3-6A1C-41B2-9665-5FF8CBD9ED4E}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B2:V114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8277,7 +8290,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -8321,7 +8334,7 @@
       </c>
       <c r="C7" s="159"/>
       <c r="D7" s="83" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -8337,7 +8350,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -8369,7 +8382,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -8385,7 +8398,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -8401,7 +8414,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="160" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E12" s="160"/>
       <c r="F12" s="160"/>
@@ -8413,43 +8426,43 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
@@ -8468,19 +8481,19 @@
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G28" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L28" s="7"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G29" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G30" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -8494,112 +8507,112 @@
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E34" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E35" s="3"/>
       <c r="F35" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F37" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E38" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E39" s="3"/>
       <c r="F39" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E40" s="3"/>
       <c r="F40" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F41" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E42" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E43" s="3"/>
       <c r="F43" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F44" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E45" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E46" s="3"/>
       <c r="F46" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E47" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E48" s="3"/>
       <c r="F48" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E49" s="3"/>
       <c r="F49" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E50" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E51" s="3"/>
       <c r="F51" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E52" s="3"/>
       <c r="F52" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="3:11" x14ac:dyDescent="0.25">
@@ -8607,7 +8620,7 @@
     </row>
     <row r="54" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E54" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="3:11" x14ac:dyDescent="0.25">
@@ -8626,19 +8639,19 @@
     </row>
     <row r="57" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F57" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K57" s="7"/>
     </row>
     <row r="58" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F58" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K58" s="7"/>
     </row>
     <row r="59" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F59" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K59" s="7"/>
     </row>
@@ -8652,50 +8665,50 @@
     </row>
     <row r="63" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
       <c r="E65" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E66" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E67" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="69" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D69" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D70" s="2"/>
       <c r="E70" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="71" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E71" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F72" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G72" s="47"/>
       <c r="H72" s="4"/>
@@ -8717,7 +8730,7 @@
     <row r="73" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F73" s="6"/>
       <c r="G73" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H73" s="24"/>
       <c r="V73" s="7"/>
@@ -8725,105 +8738,105 @@
     <row r="74" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F74" s="6"/>
       <c r="H74" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="V74" s="7"/>
     </row>
     <row r="75" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F75" s="6"/>
       <c r="H75" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="V75" s="7"/>
     </row>
     <row r="76" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F76" s="6"/>
       <c r="H76" s="24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V76" s="7"/>
     </row>
     <row r="77" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F77" s="6"/>
       <c r="H77" s="24" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V77" s="7"/>
     </row>
     <row r="78" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F78" s="6"/>
       <c r="H78" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V78" s="7"/>
     </row>
     <row r="79" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F79" s="6"/>
       <c r="H79" s="24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V79" s="7"/>
     </row>
     <row r="80" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F80" s="6"/>
       <c r="H80" s="24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V80" s="7"/>
     </row>
     <row r="81" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F81" s="6"/>
       <c r="H81" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="V81" s="7"/>
     </row>
     <row r="82" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F82" s="6"/>
       <c r="H82" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="V82" s="7"/>
     </row>
     <row r="83" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F83" s="6"/>
       <c r="H83" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="V83" s="7"/>
     </row>
     <row r="84" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F84" s="6"/>
       <c r="H84" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="V84" s="7"/>
     </row>
     <row r="85" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F85" s="6"/>
       <c r="H85" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="V85" s="7"/>
     </row>
     <row r="86" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F86" s="6"/>
       <c r="H86" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="V86" s="7"/>
     </row>
     <row r="87" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F87" s="6"/>
       <c r="H87" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V87" s="7"/>
     </row>
     <row r="88" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F88" s="6"/>
       <c r="G88" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H88" s="24"/>
       <c r="V88" s="7"/>
@@ -8831,7 +8844,7 @@
     <row r="89" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F89" s="6"/>
       <c r="G89" s="36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H89" s="24"/>
       <c r="V89" s="7"/>
@@ -8857,17 +8870,17 @@
     </row>
     <row r="92" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F92" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G93" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="94" spans="6:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G94" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="95" spans="6:22" x14ac:dyDescent="0.25">
@@ -8885,19 +8898,19 @@
     </row>
     <row r="97" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G97" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K97" s="7"/>
     </row>
     <row r="98" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G98" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K98" s="7"/>
     </row>
     <row r="99" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G99" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K99" s="7"/>
     </row>
@@ -8910,12 +8923,12 @@
     </row>
     <row r="102" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E102" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E103" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="104" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -8952,28 +8965,28 @@
     <row r="109" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K109" s="7"/>
     </row>
     <row r="110" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K110" s="7"/>
     </row>
     <row r="111" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K111" s="7"/>
     </row>
     <row r="112" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K112" s="7"/>
     </row>
@@ -9022,7 +9035,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FE3489-2390-4425-B299-7AC12373D124}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B2:S123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9033,7 +9046,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -9093,7 +9106,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -9125,7 +9138,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -9141,7 +9154,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -9157,7 +9170,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E12" s="83"/>
       <c r="F12" s="83"/>
@@ -9169,22 +9182,22 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="D16" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E17" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
@@ -9203,19 +9216,19 @@
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F20" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F21" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F22" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K22" s="7"/>
     </row>
@@ -9229,12 +9242,12 @@
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D27" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.25">
@@ -9259,7 +9272,7 @@
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E30" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F30" s="30"/>
       <c r="G30" s="30"/>
@@ -9270,7 +9283,7 @@
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E31" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F31" s="30"/>
       <c r="G31" s="30"/>
@@ -9281,7 +9294,7 @@
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E32" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
@@ -9301,7 +9314,7 @@
     </row>
     <row r="35" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D35" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.25">
@@ -9319,19 +9332,19 @@
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E38" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E39" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E40" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I40" s="7"/>
     </row>
@@ -9344,27 +9357,27 @@
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C46" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D47" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F49" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G49" s="156"/>
       <c r="H49" s="4"/>
@@ -9377,7 +9390,7 @@
     <row r="50" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F50" s="6"/>
       <c r="G50" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H50" s="24"/>
       <c r="M50" s="7"/>
@@ -9385,49 +9398,49 @@
     <row r="51" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F51" s="6"/>
       <c r="H51" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M51" s="7"/>
     </row>
     <row r="52" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F52" s="6"/>
       <c r="H52" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M52" s="7"/>
     </row>
     <row r="53" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F53" s="6"/>
       <c r="H53" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M53" s="7"/>
     </row>
     <row r="54" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F54" s="6"/>
       <c r="H54" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M54" s="7"/>
     </row>
     <row r="55" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F55" s="6"/>
       <c r="H55" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M55" s="7"/>
     </row>
     <row r="56" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F56" s="6"/>
       <c r="H56" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M56" s="7"/>
     </row>
     <row r="57" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F57" s="6"/>
       <c r="G57" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H57" s="24"/>
       <c r="M57" s="7"/>
@@ -9435,14 +9448,14 @@
     <row r="58" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F58" s="6"/>
       <c r="H58" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M58" s="7"/>
     </row>
     <row r="59" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F59" s="6"/>
       <c r="G59" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H59" s="24"/>
       <c r="M59" s="7"/>
@@ -9450,7 +9463,7 @@
     <row r="60" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F60" s="6"/>
       <c r="H60" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M60" s="7"/>
     </row>
@@ -9466,7 +9479,7 @@
     </row>
     <row r="63" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F63" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="6:16" x14ac:dyDescent="0.25">
@@ -9481,7 +9494,7 @@
       <c r="M64" s="37"/>
       <c r="N64" s="38"/>
       <c r="P64" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="5:14" x14ac:dyDescent="0.25">
@@ -9496,7 +9509,7 @@
     </row>
     <row r="66" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G66" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H66" s="39"/>
       <c r="I66" s="39"/>
@@ -9508,7 +9521,7 @@
     </row>
     <row r="67" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G67" s="43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H67" s="39"/>
       <c r="I67" s="39"/>
@@ -9520,7 +9533,7 @@
     </row>
     <row r="68" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G68" s="43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H68" s="39"/>
       <c r="I68" s="39"/>
@@ -9542,7 +9555,7 @@
     </row>
     <row r="71" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E71" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="5:14" x14ac:dyDescent="0.25">
@@ -9554,7 +9567,7 @@
       <c r="I72" s="37"/>
       <c r="J72" s="38"/>
       <c r="L72" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="5:14" x14ac:dyDescent="0.25">
@@ -9566,7 +9579,7 @@
     </row>
     <row r="74" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F74" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G74" s="39"/>
       <c r="H74" s="39"/>
@@ -9575,7 +9588,7 @@
     </row>
     <row r="75" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F75" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G75" s="39"/>
       <c r="H75" s="39"/>
@@ -9584,7 +9597,7 @@
     </row>
     <row r="76" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F76" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G76" s="39"/>
       <c r="H76" s="39"/>
@@ -9600,7 +9613,7 @@
     </row>
     <row r="79" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E79" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="5:14" x14ac:dyDescent="0.25">
@@ -9613,7 +9626,7 @@
       <c r="J80" s="37"/>
       <c r="K80" s="38"/>
       <c r="M80" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="4:12" x14ac:dyDescent="0.25">
@@ -9626,7 +9639,7 @@
     </row>
     <row r="82" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F82" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G82" s="39"/>
       <c r="H82" s="39"/>
@@ -9636,7 +9649,7 @@
     </row>
     <row r="83" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F83" s="43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G83" s="39"/>
       <c r="H83" s="39"/>
@@ -9646,7 +9659,7 @@
     </row>
     <row r="84" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F84" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G84" s="39"/>
       <c r="H84" s="39"/>
@@ -9664,17 +9677,17 @@
     </row>
     <row r="87" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E87" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D89" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="91" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E91" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="4:12" x14ac:dyDescent="0.25">
@@ -9699,7 +9712,7 @@
     </row>
     <row r="94" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F94" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="30"/>
@@ -9710,7 +9723,7 @@
     </row>
     <row r="95" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F95" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="30"/>
@@ -9721,7 +9734,7 @@
     </row>
     <row r="96" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F96" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="30"/>
@@ -9741,7 +9754,7 @@
     </row>
     <row r="99" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="4:12" x14ac:dyDescent="0.25">
@@ -9766,7 +9779,7 @@
     </row>
     <row r="102" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F102" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="30"/>
@@ -9777,7 +9790,7 @@
     </row>
     <row r="103" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F103" s="34" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G103" s="30"/>
       <c r="H103" s="30"/>
@@ -9788,7 +9801,7 @@
     </row>
     <row r="104" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F104" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G104" s="30"/>
       <c r="H104" s="30"/>
@@ -9808,7 +9821,7 @@
     </row>
     <row r="107" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E107" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="109" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -9844,56 +9857,56 @@
     <row r="114" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J114" s="7"/>
     </row>
     <row r="115" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J115" s="7"/>
     </row>
     <row r="116" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J116" s="7"/>
     </row>
     <row r="117" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J117" s="7"/>
     </row>
     <row r="118" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J118" s="7"/>
     </row>
     <row r="119" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J119" s="7"/>
     </row>
     <row r="120" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J120" s="7"/>
     </row>
     <row r="121" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J121" s="7"/>
     </row>
@@ -9947,7 +9960,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E9BD5A-136D-44FB-8299-CDB0B621D144}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B2:S116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9958,7 +9971,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -10002,7 +10015,7 @@
       </c>
       <c r="C7" s="159"/>
       <c r="D7" s="83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -10018,7 +10031,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -10050,7 +10063,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -10066,7 +10079,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -10082,7 +10095,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E12" s="83"/>
       <c r="F12" s="83"/>
@@ -10094,28 +10107,28 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F18" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
@@ -10134,19 +10147,19 @@
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G21" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L21" s="7"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G22" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L22" s="7"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G23" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L23" s="7"/>
     </row>
@@ -10160,7 +10173,7 @@
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D26" s="54" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E26" s="55"/>
       <c r="F26" s="55"/>
@@ -10168,7 +10181,7 @@
     <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D27" s="55"/>
       <c r="E27" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F27" s="55"/>
     </row>
@@ -10176,27 +10189,27 @@
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
       <c r="F28" s="55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E32" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F33" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G33" s="156"/>
       <c r="H33" s="4"/>
@@ -10209,7 +10222,7 @@
     <row r="34" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F34" s="6"/>
       <c r="G34" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H34" s="24"/>
       <c r="M34" s="7"/>
@@ -10217,49 +10230,49 @@
     <row r="35" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F35" s="6"/>
       <c r="H35" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M35" s="7"/>
     </row>
     <row r="36" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F36" s="6"/>
       <c r="H36" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M36" s="7"/>
     </row>
     <row r="37" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F37" s="6"/>
       <c r="H37" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M37" s="7"/>
     </row>
     <row r="38" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F38" s="6"/>
       <c r="H38" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M38" s="7"/>
     </row>
     <row r="39" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F39" s="6"/>
       <c r="H39" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M39" s="7"/>
     </row>
     <row r="40" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
       <c r="H40" s="24" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M40" s="7"/>
     </row>
     <row r="41" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F41" s="6"/>
       <c r="G41" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H41" s="24"/>
       <c r="M41" s="7"/>
@@ -10267,14 +10280,14 @@
     <row r="42" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F42" s="6"/>
       <c r="H42" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M42" s="7"/>
     </row>
     <row r="43" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F43" s="6"/>
       <c r="G43" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H43" s="24"/>
       <c r="M43" s="7"/>
@@ -10282,7 +10295,7 @@
     <row r="44" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F44" s="6"/>
       <c r="H44" s="24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M44" s="7"/>
     </row>
@@ -10298,7 +10311,7 @@
     </row>
     <row r="47" spans="6:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F47" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="6:14" x14ac:dyDescent="0.25">
@@ -10325,7 +10338,7 @@
     </row>
     <row r="50" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G50" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H50" s="39"/>
       <c r="I50" s="39"/>
@@ -10337,7 +10350,7 @@
     </row>
     <row r="51" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G51" s="43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
@@ -10349,7 +10362,7 @@
     </row>
     <row r="52" spans="5:14" x14ac:dyDescent="0.25">
       <c r="G52" s="43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H52" s="39"/>
       <c r="I52" s="39"/>
@@ -10371,7 +10384,7 @@
     </row>
     <row r="55" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E55" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="5:14" x14ac:dyDescent="0.25">
@@ -10392,7 +10405,7 @@
     </row>
     <row r="58" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F58" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G58" s="39"/>
       <c r="H58" s="39"/>
@@ -10401,7 +10414,7 @@
     </row>
     <row r="59" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F59" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G59" s="39"/>
       <c r="H59" s="39"/>
@@ -10410,7 +10423,7 @@
     </row>
     <row r="60" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F60" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G60" s="39"/>
       <c r="H60" s="39"/>
@@ -10426,7 +10439,7 @@
     </row>
     <row r="63" spans="5:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E63" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="5:14" x14ac:dyDescent="0.25">
@@ -10449,7 +10462,7 @@
     </row>
     <row r="66" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F66" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G66" s="39"/>
       <c r="H66" s="39"/>
@@ -10459,7 +10472,7 @@
     </row>
     <row r="67" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F67" s="43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G67" s="39"/>
       <c r="H67" s="39"/>
@@ -10469,7 +10482,7 @@
     </row>
     <row r="68" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F68" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G68" s="39"/>
       <c r="H68" s="39"/>
@@ -10487,17 +10500,17 @@
     </row>
     <row r="71" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E71" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D73" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="4:12" x14ac:dyDescent="0.25">
@@ -10522,7 +10535,7 @@
     </row>
     <row r="78" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F78" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -10533,7 +10546,7 @@
     </row>
     <row r="79" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F79" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
@@ -10544,7 +10557,7 @@
     </row>
     <row r="80" spans="4:12" x14ac:dyDescent="0.25">
       <c r="F80" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G80" s="30"/>
       <c r="H80" s="30"/>
@@ -10564,7 +10577,7 @@
     </row>
     <row r="83" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E83" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="5:12" x14ac:dyDescent="0.25">
@@ -10589,7 +10602,7 @@
     </row>
     <row r="86" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F86" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G86" s="30"/>
       <c r="H86" s="30"/>
@@ -10600,7 +10613,7 @@
     </row>
     <row r="87" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F87" s="34" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
@@ -10611,7 +10624,7 @@
     </row>
     <row r="88" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F88" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G88" s="30"/>
       <c r="H88" s="30"/>
@@ -10631,7 +10644,7 @@
     </row>
     <row r="91" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E91" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" spans="5:12" x14ac:dyDescent="0.25">
@@ -10656,7 +10669,7 @@
     </row>
     <row r="94" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F94" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="30"/>
@@ -10667,7 +10680,7 @@
     </row>
     <row r="95" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F95" s="34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="30"/>
@@ -10678,7 +10691,7 @@
     </row>
     <row r="96" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F96" s="34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="30"/>
@@ -10698,12 +10711,12 @@
     </row>
     <row r="99" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E99" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E100" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -10739,56 +10752,56 @@
     <row r="107" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J107" s="7"/>
     </row>
     <row r="108" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J108" s="7"/>
     </row>
     <row r="109" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J109" s="7"/>
     </row>
     <row r="110" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J110" s="7"/>
     </row>
     <row r="111" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J111" s="7"/>
     </row>
     <row r="112" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J112" s="7"/>
     </row>
     <row r="113" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J113" s="7"/>
     </row>
     <row r="114" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J114" s="7"/>
     </row>
@@ -11052,7 +11065,7 @@
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
       <c r="G7" s="69" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H7" s="69"/>
       <c r="I7" s="69"/>
@@ -11077,7 +11090,7 @@
       <c r="E8" s="69"/>
       <c r="F8" s="69"/>
       <c r="G8" s="69" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H8" s="69"/>
       <c r="I8" s="69"/>
@@ -11102,7 +11115,7 @@
       <c r="E9" s="69"/>
       <c r="F9" s="69"/>
       <c r="G9" s="69" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H9" s="69"/>
       <c r="I9" s="69"/>
@@ -11152,7 +11165,7 @@
       <c r="E11" s="69"/>
       <c r="F11" s="69"/>
       <c r="G11" s="69" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H11" s="69"/>
       <c r="I11" s="69"/>
@@ -11177,7 +11190,7 @@
       <c r="E12" s="69"/>
       <c r="F12" s="69"/>
       <c r="G12" s="69" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H12" s="69"/>
       <c r="I12" s="69"/>
@@ -11202,7 +11215,7 @@
       <c r="E13" s="69"/>
       <c r="F13" s="69"/>
       <c r="G13" s="69" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H13" s="69"/>
       <c r="I13" s="69"/>
@@ -11277,7 +11290,7 @@
       <c r="E16" s="69"/>
       <c r="F16" s="69"/>
       <c r="G16" s="69" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H16" s="69"/>
       <c r="I16" s="69"/>
@@ -11352,7 +11365,7 @@
       <c r="E19" s="69"/>
       <c r="F19" s="69"/>
       <c r="G19" s="69" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H19" s="69"/>
       <c r="I19" s="69"/>
@@ -11377,7 +11390,7 @@
       <c r="E20" s="69"/>
       <c r="F20" s="69"/>
       <c r="G20" s="69" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H20" s="69"/>
       <c r="I20" s="69"/>
@@ -11402,7 +11415,7 @@
       <c r="E21" s="69"/>
       <c r="F21" s="69"/>
       <c r="G21" s="69" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H21" s="69"/>
       <c r="I21" s="69"/>
@@ -11427,7 +11440,7 @@
       <c r="E22" s="69"/>
       <c r="F22" s="69"/>
       <c r="G22" s="74" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H22" s="69"/>
       <c r="I22" s="69"/>
@@ -11446,13 +11459,13 @@
     </row>
     <row r="23" spans="3:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="69" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D23" s="69"/>
       <c r="E23" s="69"/>
       <c r="F23" s="69"/>
       <c r="G23" s="74" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H23" s="69"/>
       <c r="I23" s="69"/>
@@ -11477,7 +11490,7 @@
       <c r="E24" s="69"/>
       <c r="F24" s="69"/>
       <c r="G24" s="69" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H24" s="69"/>
       <c r="I24" s="69"/>
@@ -11552,7 +11565,7 @@
       <c r="E27" s="69"/>
       <c r="F27" s="69"/>
       <c r="G27" s="69" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H27" s="69"/>
       <c r="I27" s="69"/>
@@ -11577,7 +11590,7 @@
       <c r="E28" s="69"/>
       <c r="F28" s="69"/>
       <c r="G28" s="69" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H28" s="69"/>
       <c r="I28" s="69"/>
@@ -12088,7 +12101,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA96B6B-2048-4344-A13F-226F7AADB2AE}">
-  <dimension ref="B1:AI59"/>
+  <dimension ref="B1:AI61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="9.140625" style="1"/>
@@ -12244,11 +12257,11 @@
       </c>
       <c r="H7" s="100"/>
       <c r="I7" s="99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J7" s="100"/>
       <c r="K7" s="101" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L7" s="102"/>
       <c r="M7" s="102"/>
@@ -12271,7 +12284,7 @@
     </row>
     <row r="8" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" s="112"/>
       <c r="D8" s="112"/>
@@ -12282,11 +12295,11 @@
       </c>
       <c r="H8" s="106"/>
       <c r="I8" s="99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J8" s="100"/>
       <c r="K8" s="109" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L8" s="110"/>
       <c r="M8" s="110"/>
@@ -12316,7 +12329,7 @@
     </row>
     <row r="9" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" s="112"/>
       <c r="D9" s="112"/>
@@ -12327,11 +12340,11 @@
       </c>
       <c r="H9" s="106"/>
       <c r="I9" s="99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J9" s="100"/>
       <c r="K9" s="109" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L9" s="110"/>
       <c r="M9" s="110"/>
@@ -12359,7 +12372,7 @@
     </row>
     <row r="10" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="115" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C10" s="116"/>
       <c r="D10" s="116"/>
@@ -12370,7 +12383,7 @@
       </c>
       <c r="H10" s="119"/>
       <c r="I10" s="120" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J10" s="121"/>
       <c r="K10" s="127"/>
@@ -12400,7 +12413,7 @@
     </row>
     <row r="11" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C11" s="112"/>
       <c r="D11" s="112"/>
@@ -12411,11 +12424,11 @@
       </c>
       <c r="H11" s="106"/>
       <c r="I11" s="99" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J11" s="100"/>
       <c r="K11" s="109" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L11" s="110"/>
       <c r="M11" s="110"/>
@@ -12443,7 +12456,7 @@
     </row>
     <row r="12" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="111" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" s="112"/>
       <c r="D12" s="112"/>
@@ -12454,11 +12467,11 @@
       </c>
       <c r="H12" s="106"/>
       <c r="I12" s="99" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J12" s="100"/>
       <c r="K12" s="107" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L12" s="108"/>
       <c r="M12" s="108"/>
@@ -12480,13 +12493,13 @@
       <c r="AA12" s="67"/>
       <c r="AC12" s="6"/>
       <c r="AD12" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AI12" s="7"/>
     </row>
     <row r="13" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="115" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C13" s="116"/>
       <c r="D13" s="116"/>
@@ -12497,7 +12510,7 @@
       </c>
       <c r="H13" s="119"/>
       <c r="I13" s="120" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J13" s="121"/>
       <c r="K13" s="122"/>
@@ -12527,7 +12540,7 @@
     </row>
     <row r="14" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" s="112"/>
       <c r="D14" s="112"/>
@@ -12538,11 +12551,11 @@
       </c>
       <c r="H14" s="106"/>
       <c r="I14" s="99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J14" s="100"/>
       <c r="K14" s="107" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L14" s="108"/>
       <c r="M14" s="108"/>
@@ -12564,13 +12577,13 @@
       <c r="AA14" s="67"/>
       <c r="AC14" s="6"/>
       <c r="AD14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AI14" s="7"/>
     </row>
     <row r="15" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="111" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" s="112"/>
       <c r="D15" s="112"/>
@@ -12581,11 +12594,11 @@
       </c>
       <c r="H15" s="106"/>
       <c r="I15" s="99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J15" s="100"/>
       <c r="K15" s="109" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L15" s="110"/>
       <c r="M15" s="110"/>
@@ -12613,7 +12626,7 @@
     </row>
     <row r="16" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="111" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" s="112"/>
       <c r="D16" s="112"/>
@@ -12624,11 +12637,11 @@
       </c>
       <c r="H16" s="106"/>
       <c r="I16" s="99" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J16" s="100"/>
       <c r="K16" s="109" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L16" s="110"/>
       <c r="M16" s="110"/>
@@ -12656,7 +12669,7 @@
     </row>
     <row r="17" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="103" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C17" s="104"/>
       <c r="D17" s="104"/>
@@ -12669,11 +12682,11 @@
       </c>
       <c r="H17" s="106"/>
       <c r="I17" s="99" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J17" s="100"/>
       <c r="K17" s="107" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L17" s="108"/>
       <c r="M17" s="108"/>
@@ -12701,7 +12714,7 @@
     </row>
     <row r="18" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C18" s="112"/>
       <c r="D18" s="112"/>
@@ -12714,11 +12727,11 @@
       </c>
       <c r="H18" s="106"/>
       <c r="I18" s="99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J18" s="100"/>
       <c r="K18" s="107" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L18" s="108"/>
       <c r="M18" s="108"/>
@@ -12746,7 +12759,7 @@
     </row>
     <row r="19" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C19" s="112"/>
       <c r="D19" s="112"/>
@@ -12759,11 +12772,11 @@
       </c>
       <c r="H19" s="106"/>
       <c r="I19" s="99" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J19" s="100"/>
       <c r="K19" s="109" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L19" s="110"/>
       <c r="M19" s="110"/>
@@ -12791,7 +12804,7 @@
     </row>
     <row r="20" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C20" s="112"/>
       <c r="D20" s="112"/>
@@ -12804,11 +12817,11 @@
       </c>
       <c r="H20" s="106"/>
       <c r="I20" s="99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J20" s="100"/>
       <c r="K20" s="107" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L20" s="108"/>
       <c r="M20" s="108"/>
@@ -12849,11 +12862,11 @@
       </c>
       <c r="H21" s="106"/>
       <c r="I21" s="99" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J21" s="100"/>
       <c r="K21" s="107" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L21" s="108"/>
       <c r="M21" s="108"/>
@@ -12894,11 +12907,11 @@
       </c>
       <c r="H22" s="106"/>
       <c r="I22" s="99" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J22" s="100"/>
       <c r="K22" s="109" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="L22" s="110"/>
       <c r="M22" s="110"/>
@@ -12926,7 +12939,7 @@
     </row>
     <row r="23" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="103" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="104"/>
       <c r="D23" s="104"/>
@@ -12939,11 +12952,11 @@
       </c>
       <c r="H23" s="106"/>
       <c r="I23" s="99" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J23" s="100"/>
       <c r="K23" s="109" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L23" s="110"/>
       <c r="M23" s="110"/>
@@ -12971,7 +12984,7 @@
     </row>
     <row r="24" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="134" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" s="97"/>
       <c r="D24" s="97"/>
@@ -12984,11 +12997,11 @@
       </c>
       <c r="H24" s="106"/>
       <c r="I24" s="99" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J24" s="100"/>
       <c r="K24" s="109" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="L24" s="110"/>
       <c r="M24" s="110"/>
@@ -13016,7 +13029,7 @@
     </row>
     <row r="25" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="103" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" s="104"/>
       <c r="D25" s="104"/>
@@ -13029,11 +13042,11 @@
       </c>
       <c r="H25" s="106"/>
       <c r="I25" s="99" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J25" s="100"/>
       <c r="K25" s="107" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L25" s="108"/>
       <c r="M25" s="108"/>
@@ -13076,10 +13089,12 @@
       </c>
       <c r="H26" s="106"/>
       <c r="I26" s="99" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J26" s="100"/>
-      <c r="K26" s="107"/>
+      <c r="K26" s="107" t="s">
+        <v>479</v>
+      </c>
       <c r="L26" s="108"/>
       <c r="M26" s="108"/>
       <c r="N26" s="108"/>
@@ -13110,14 +13125,16 @@
         <v>11</v>
       </c>
       <c r="G27" s="105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H27" s="106"/>
       <c r="I27" s="99" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J27" s="100"/>
-      <c r="K27" s="107"/>
+      <c r="K27" s="107" t="s">
+        <v>501</v>
+      </c>
       <c r="L27" s="108"/>
       <c r="M27" s="108"/>
       <c r="N27" s="108"/>
@@ -13138,24 +13155,26 @@
       <c r="AA27" s="67"/>
     </row>
     <row r="28" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="103" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="71"/>
+      <c r="B28" s="134" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="98"/>
       <c r="F28" s="14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G28" s="105">
         <v>400</v>
       </c>
       <c r="H28" s="106"/>
       <c r="I28" s="99" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J28" s="100"/>
-      <c r="K28" s="107"/>
+      <c r="K28" s="107" t="s">
+        <v>480</v>
+      </c>
       <c r="L28" s="108"/>
       <c r="M28" s="108"/>
       <c r="N28" s="108"/>
@@ -13177,23 +13196,25 @@
     </row>
     <row r="29" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="103" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C29" s="104"/>
       <c r="D29" s="104"/>
       <c r="E29" s="71"/>
       <c r="F29" s="14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G29" s="105">
         <v>400</v>
       </c>
       <c r="H29" s="106"/>
       <c r="I29" s="99" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J29" s="100"/>
-      <c r="K29" s="107"/>
+      <c r="K29" s="107" t="s">
+        <v>481</v>
+      </c>
       <c r="L29" s="108"/>
       <c r="M29" s="108"/>
       <c r="N29" s="108"/>
@@ -13215,7 +13236,7 @@
     </row>
     <row r="30" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="103" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C30" s="104"/>
       <c r="D30" s="104"/>
@@ -13224,11 +13245,11 @@
         <v>7</v>
       </c>
       <c r="G30" s="105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H30" s="106"/>
       <c r="I30" s="99" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J30" s="100"/>
       <c r="K30" s="107"/>
@@ -13252,28 +13273,30 @@
       <c r="AA30" s="67"/>
     </row>
     <row r="31" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="111" t="s">
-        <v>389</v>
-      </c>
-      <c r="C31" s="112"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="14"/>
+      <c r="B31" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="G31" s="105">
         <v>400</v>
       </c>
       <c r="H31" s="106"/>
       <c r="I31" s="99" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J31" s="100"/>
-      <c r="K31" s="109"/>
-      <c r="L31" s="110"/>
-      <c r="M31" s="110"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="110"/>
-      <c r="P31" s="110"/>
-      <c r="Q31" s="133"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="108"/>
+      <c r="O31" s="108"/>
+      <c r="P31" s="108"/>
+      <c r="Q31" s="108"/>
       <c r="R31" s="114"/>
       <c r="S31" s="110"/>
       <c r="T31" s="110"/>
@@ -13281,7 +13304,7 @@
       <c r="V31" s="110"/>
       <c r="W31" s="110"/>
       <c r="X31" s="110"/>
-      <c r="Y31" s="133"/>
+      <c r="Y31" s="110"/>
       <c r="Z31" s="67" t="s">
         <v>4</v>
       </c>
@@ -13289,7 +13312,7 @@
     </row>
     <row r="32" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="103" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C32" s="104"/>
       <c r="D32" s="104"/>
@@ -13298,11 +13321,11 @@
         <v>7</v>
       </c>
       <c r="G32" s="105">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H32" s="106"/>
       <c r="I32" s="99" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J32" s="100"/>
       <c r="K32" s="107"/>
@@ -13311,36 +13334,34 @@
       <c r="N32" s="108"/>
       <c r="O32" s="108"/>
       <c r="P32" s="108"/>
-      <c r="Q32" s="137"/>
+      <c r="Q32" s="108"/>
       <c r="R32" s="114"/>
-      <c r="S32" s="135"/>
-      <c r="T32" s="135"/>
-      <c r="U32" s="135"/>
-      <c r="V32" s="135"/>
-      <c r="W32" s="135"/>
-      <c r="X32" s="135"/>
-      <c r="Y32" s="136"/>
+      <c r="S32" s="110"/>
+      <c r="T32" s="110"/>
+      <c r="U32" s="110"/>
+      <c r="V32" s="110"/>
+      <c r="W32" s="110"/>
+      <c r="X32" s="110"/>
+      <c r="Y32" s="110"/>
       <c r="Z32" s="67" t="s">
         <v>4</v>
       </c>
       <c r="AA32" s="67"/>
     </row>
     <row r="33" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="103" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="104"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="14" t="s">
-        <v>7</v>
-      </c>
+      <c r="B33" s="111" t="s">
+        <v>387</v>
+      </c>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="105">
         <v>400</v>
       </c>
       <c r="H33" s="106"/>
       <c r="I33" s="99" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J33" s="100"/>
       <c r="K33" s="109"/>
@@ -13365,7 +13386,7 @@
     </row>
     <row r="34" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="103" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="104"/>
       <c r="D34" s="104"/>
@@ -13374,58 +13395,58 @@
         <v>7</v>
       </c>
       <c r="G34" s="105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H34" s="106"/>
       <c r="I34" s="99" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J34" s="100"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="110"/>
-      <c r="M34" s="110"/>
-      <c r="N34" s="110"/>
-      <c r="O34" s="110"/>
-      <c r="P34" s="110"/>
-      <c r="Q34" s="133"/>
+      <c r="K34" s="107"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="Q34" s="137"/>
       <c r="R34" s="114"/>
-      <c r="S34" s="110"/>
-      <c r="T34" s="110"/>
-      <c r="U34" s="110"/>
-      <c r="V34" s="110"/>
-      <c r="W34" s="110"/>
-      <c r="X34" s="110"/>
-      <c r="Y34" s="133"/>
+      <c r="S34" s="135"/>
+      <c r="T34" s="135"/>
+      <c r="U34" s="135"/>
+      <c r="V34" s="135"/>
+      <c r="W34" s="135"/>
+      <c r="X34" s="135"/>
+      <c r="Y34" s="136"/>
       <c r="Z34" s="67" t="s">
         <v>4</v>
       </c>
       <c r="AA34" s="67"/>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="103" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C35" s="104"/>
       <c r="D35" s="104"/>
       <c r="E35" s="71"/>
       <c r="F35" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G35" s="105">
         <v>400</v>
       </c>
       <c r="H35" s="106"/>
       <c r="I35" s="99" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J35" s="100"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="108"/>
-      <c r="N35" s="108"/>
-      <c r="O35" s="108"/>
-      <c r="P35" s="108"/>
-      <c r="Q35" s="108"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="110"/>
+      <c r="M35" s="110"/>
+      <c r="N35" s="110"/>
+      <c r="O35" s="110"/>
+      <c r="P35" s="110"/>
+      <c r="Q35" s="133"/>
       <c r="R35" s="114"/>
       <c r="S35" s="110"/>
       <c r="T35" s="110"/>
@@ -13439,31 +13460,31 @@
       </c>
       <c r="AA35" s="67"/>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="103" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C36" s="104"/>
       <c r="D36" s="104"/>
       <c r="E36" s="71"/>
       <c r="F36" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G36" s="105">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H36" s="106"/>
       <c r="I36" s="99" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J36" s="100"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="108"/>
-      <c r="N36" s="108"/>
-      <c r="O36" s="108"/>
-      <c r="P36" s="108"/>
-      <c r="Q36" s="108"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="110"/>
+      <c r="N36" s="110"/>
+      <c r="O36" s="110"/>
+      <c r="P36" s="110"/>
+      <c r="Q36" s="133"/>
       <c r="R36" s="114"/>
       <c r="S36" s="110"/>
       <c r="T36" s="110"/>
@@ -13471,7 +13492,7 @@
       <c r="V36" s="110"/>
       <c r="W36" s="110"/>
       <c r="X36" s="110"/>
-      <c r="Y36" s="110"/>
+      <c r="Y36" s="133"/>
       <c r="Z36" s="67" t="s">
         <v>4</v>
       </c>
@@ -13488,11 +13509,11 @@
         <v>11</v>
       </c>
       <c r="G37" s="105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H37" s="106"/>
       <c r="I37" s="99" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J37" s="100"/>
       <c r="K37" s="107"/>
@@ -13509,7 +13530,7 @@
       <c r="V37" s="110"/>
       <c r="W37" s="110"/>
       <c r="X37" s="110"/>
-      <c r="Y37" s="110"/>
+      <c r="Y37" s="133"/>
       <c r="Z37" s="67" t="s">
         <v>4</v>
       </c>
@@ -13517,7 +13538,7 @@
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" s="103" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C38" s="104"/>
       <c r="D38" s="104"/>
@@ -13530,7 +13551,7 @@
       </c>
       <c r="H38" s="106"/>
       <c r="I38" s="99" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J38" s="100"/>
       <c r="K38" s="107"/>
@@ -13555,7 +13576,7 @@
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="103" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C39" s="104"/>
       <c r="D39" s="104"/>
@@ -13564,11 +13585,11 @@
         <v>11</v>
       </c>
       <c r="G39" s="105">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H39" s="106"/>
       <c r="I39" s="99" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J39" s="100"/>
       <c r="K39" s="107"/>
@@ -13593,7 +13614,7 @@
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" s="104"/>
       <c r="D40" s="104"/>
@@ -13602,43 +13623,51 @@
         <v>11</v>
       </c>
       <c r="G40" s="105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H40" s="106"/>
       <c r="I40" s="99" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J40" s="100"/>
-      <c r="K40" s="109"/>
-      <c r="L40" s="110"/>
-      <c r="M40" s="110"/>
-      <c r="N40" s="110"/>
-      <c r="O40" s="110"/>
-      <c r="P40" s="110"/>
-      <c r="Q40" s="133"/>
-      <c r="R40" s="109"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
+      <c r="O40" s="108"/>
+      <c r="P40" s="108"/>
+      <c r="Q40" s="108"/>
+      <c r="R40" s="114"/>
       <c r="S40" s="110"/>
       <c r="T40" s="110"/>
       <c r="U40" s="110"/>
       <c r="V40" s="110"/>
       <c r="W40" s="110"/>
       <c r="X40" s="110"/>
-      <c r="Y40" s="133"/>
+      <c r="Y40" s="110"/>
       <c r="Z40" s="67" t="s">
         <v>4</v>
       </c>
       <c r="AA40" s="67"/>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B41" s="103"/>
+      <c r="B41" s="103" t="s">
+        <v>145</v>
+      </c>
       <c r="C41" s="104"/>
       <c r="D41" s="104"/>
       <c r="E41" s="71"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="105"/>
+      <c r="F41" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="105">
+        <v>400</v>
+      </c>
       <c r="H41" s="106"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="106"/>
+      <c r="I41" s="99" t="s">
+        <v>508</v>
+      </c>
+      <c r="J41" s="100"/>
       <c r="K41" s="107"/>
       <c r="L41" s="108"/>
       <c r="M41" s="108"/>
@@ -13654,35 +13683,47 @@
       <c r="W41" s="110"/>
       <c r="X41" s="110"/>
       <c r="Y41" s="110"/>
-      <c r="Z41" s="67"/>
+      <c r="Z41" s="67" t="s">
+        <v>4</v>
+      </c>
       <c r="AA41" s="67"/>
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B42" s="103"/>
+      <c r="B42" s="103" t="s">
+        <v>145</v>
+      </c>
       <c r="C42" s="104"/>
       <c r="D42" s="104"/>
       <c r="E42" s="71"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="105"/>
+      <c r="F42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="105">
+        <v>500</v>
+      </c>
       <c r="H42" s="106"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="106"/>
+      <c r="I42" s="99" t="s">
+        <v>509</v>
+      </c>
+      <c r="J42" s="100"/>
       <c r="K42" s="109"/>
       <c r="L42" s="110"/>
       <c r="M42" s="110"/>
       <c r="N42" s="110"/>
       <c r="O42" s="110"/>
       <c r="P42" s="110"/>
-      <c r="Q42" s="110"/>
-      <c r="R42" s="114"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="109"/>
       <c r="S42" s="110"/>
       <c r="T42" s="110"/>
       <c r="U42" s="110"/>
       <c r="V42" s="110"/>
       <c r="W42" s="110"/>
       <c r="X42" s="110"/>
-      <c r="Y42" s="110"/>
-      <c r="Z42" s="67"/>
+      <c r="Y42" s="133"/>
+      <c r="Z42" s="67" t="s">
+        <v>4</v>
+      </c>
       <c r="AA42" s="67"/>
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
@@ -13695,13 +13736,13 @@
       <c r="H43" s="106"/>
       <c r="I43" s="105"/>
       <c r="J43" s="106"/>
-      <c r="K43" s="109"/>
-      <c r="L43" s="110"/>
-      <c r="M43" s="110"/>
-      <c r="N43" s="110"/>
-      <c r="O43" s="110"/>
-      <c r="P43" s="110"/>
-      <c r="Q43" s="110"/>
+      <c r="K43" s="107"/>
+      <c r="L43" s="108"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="108"/>
+      <c r="Q43" s="108"/>
       <c r="R43" s="114"/>
       <c r="S43" s="110"/>
       <c r="T43" s="110"/>
@@ -13729,19 +13770,19 @@
       <c r="N44" s="110"/>
       <c r="O44" s="110"/>
       <c r="P44" s="110"/>
-      <c r="Q44" s="133"/>
-      <c r="R44" s="109"/>
+      <c r="Q44" s="110"/>
+      <c r="R44" s="114"/>
       <c r="S44" s="110"/>
       <c r="T44" s="110"/>
       <c r="U44" s="110"/>
       <c r="V44" s="110"/>
       <c r="W44" s="110"/>
       <c r="X44" s="110"/>
-      <c r="Y44" s="133"/>
+      <c r="Y44" s="110"/>
       <c r="Z44" s="67"/>
       <c r="AA44" s="67"/>
     </row>
-    <row r="45" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="103"/>
       <c r="C45" s="104"/>
       <c r="D45" s="104"/>
@@ -13769,7 +13810,7 @@
       <c r="Z45" s="67"/>
       <c r="AA45" s="67"/>
     </row>
-    <row r="46" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="103"/>
       <c r="C46" s="104"/>
       <c r="D46" s="104"/>
@@ -13785,19 +13826,19 @@
       <c r="N46" s="110"/>
       <c r="O46" s="110"/>
       <c r="P46" s="110"/>
-      <c r="Q46" s="110"/>
-      <c r="R46" s="114"/>
+      <c r="Q46" s="133"/>
+      <c r="R46" s="109"/>
       <c r="S46" s="110"/>
       <c r="T46" s="110"/>
       <c r="U46" s="110"/>
       <c r="V46" s="110"/>
       <c r="W46" s="110"/>
       <c r="X46" s="110"/>
-      <c r="Y46" s="110"/>
+      <c r="Y46" s="133"/>
       <c r="Z46" s="67"/>
       <c r="AA46" s="67"/>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="103"/>
       <c r="C47" s="104"/>
       <c r="D47" s="104"/>
@@ -13813,19 +13854,19 @@
       <c r="N47" s="110"/>
       <c r="O47" s="110"/>
       <c r="P47" s="110"/>
-      <c r="Q47" s="133"/>
-      <c r="R47" s="109"/>
+      <c r="Q47" s="110"/>
+      <c r="R47" s="114"/>
       <c r="S47" s="110"/>
       <c r="T47" s="110"/>
       <c r="U47" s="110"/>
       <c r="V47" s="110"/>
       <c r="W47" s="110"/>
       <c r="X47" s="110"/>
-      <c r="Y47" s="133"/>
+      <c r="Y47" s="110"/>
       <c r="Z47" s="67"/>
       <c r="AA47" s="67"/>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="103"/>
       <c r="C48" s="104"/>
       <c r="D48" s="104"/>
@@ -13869,15 +13910,15 @@
       <c r="N49" s="110"/>
       <c r="O49" s="110"/>
       <c r="P49" s="110"/>
-      <c r="Q49" s="110"/>
-      <c r="R49" s="114"/>
+      <c r="Q49" s="133"/>
+      <c r="R49" s="109"/>
       <c r="S49" s="110"/>
       <c r="T49" s="110"/>
       <c r="U49" s="110"/>
       <c r="V49" s="110"/>
       <c r="W49" s="110"/>
       <c r="X49" s="110"/>
-      <c r="Y49" s="110"/>
+      <c r="Y49" s="133"/>
       <c r="Z49" s="67"/>
       <c r="AA49" s="67"/>
     </row>
@@ -13891,13 +13932,13 @@
       <c r="H50" s="106"/>
       <c r="I50" s="105"/>
       <c r="J50" s="106"/>
-      <c r="K50" s="107"/>
-      <c r="L50" s="108"/>
-      <c r="M50" s="108"/>
-      <c r="N50" s="108"/>
-      <c r="O50" s="108"/>
-      <c r="P50" s="108"/>
-      <c r="Q50" s="108"/>
+      <c r="K50" s="109"/>
+      <c r="L50" s="110"/>
+      <c r="M50" s="110"/>
+      <c r="N50" s="110"/>
+      <c r="O50" s="110"/>
+      <c r="P50" s="110"/>
+      <c r="Q50" s="110"/>
       <c r="R50" s="114"/>
       <c r="S50" s="110"/>
       <c r="T50" s="110"/>
@@ -13909,7 +13950,7 @@
       <c r="Z50" s="67"/>
       <c r="AA50" s="67"/>
     </row>
-    <row r="51" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="103"/>
       <c r="C51" s="104"/>
       <c r="D51" s="104"/>
@@ -13925,15 +13966,15 @@
       <c r="N51" s="110"/>
       <c r="O51" s="110"/>
       <c r="P51" s="110"/>
-      <c r="Q51" s="133"/>
-      <c r="R51" s="109"/>
+      <c r="Q51" s="110"/>
+      <c r="R51" s="114"/>
       <c r="S51" s="110"/>
       <c r="T51" s="110"/>
       <c r="U51" s="110"/>
       <c r="V51" s="110"/>
       <c r="W51" s="110"/>
       <c r="X51" s="110"/>
-      <c r="Y51" s="133"/>
+      <c r="Y51" s="110"/>
       <c r="Z51" s="67"/>
       <c r="AA51" s="67"/>
     </row>
@@ -13965,7 +14006,7 @@
       <c r="Z52" s="67"/>
       <c r="AA52" s="67"/>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="103"/>
       <c r="C53" s="104"/>
       <c r="D53" s="104"/>
@@ -13975,21 +14016,21 @@
       <c r="H53" s="106"/>
       <c r="I53" s="105"/>
       <c r="J53" s="106"/>
-      <c r="K53" s="107"/>
-      <c r="L53" s="108"/>
-      <c r="M53" s="108"/>
-      <c r="N53" s="108"/>
-      <c r="O53" s="108"/>
-      <c r="P53" s="108"/>
-      <c r="Q53" s="108"/>
-      <c r="R53" s="114"/>
+      <c r="K53" s="109"/>
+      <c r="L53" s="110"/>
+      <c r="M53" s="110"/>
+      <c r="N53" s="110"/>
+      <c r="O53" s="110"/>
+      <c r="P53" s="110"/>
+      <c r="Q53" s="133"/>
+      <c r="R53" s="109"/>
       <c r="S53" s="110"/>
       <c r="T53" s="110"/>
       <c r="U53" s="110"/>
       <c r="V53" s="110"/>
       <c r="W53" s="110"/>
       <c r="X53" s="110"/>
-      <c r="Y53" s="110"/>
+      <c r="Y53" s="133"/>
       <c r="Z53" s="67"/>
       <c r="AA53" s="67"/>
     </row>
@@ -14003,21 +14044,21 @@
       <c r="H54" s="106"/>
       <c r="I54" s="105"/>
       <c r="J54" s="106"/>
-      <c r="K54" s="109"/>
-      <c r="L54" s="110"/>
-      <c r="M54" s="110"/>
-      <c r="N54" s="110"/>
-      <c r="O54" s="110"/>
-      <c r="P54" s="110"/>
-      <c r="Q54" s="133"/>
-      <c r="R54" s="109"/>
+      <c r="K54" s="107"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+      <c r="N54" s="108"/>
+      <c r="O54" s="108"/>
+      <c r="P54" s="108"/>
+      <c r="Q54" s="108"/>
+      <c r="R54" s="114"/>
       <c r="S54" s="110"/>
       <c r="T54" s="110"/>
       <c r="U54" s="110"/>
       <c r="V54" s="110"/>
       <c r="W54" s="110"/>
       <c r="X54" s="110"/>
-      <c r="Y54" s="133"/>
+      <c r="Y54" s="110"/>
       <c r="Z54" s="67"/>
       <c r="AA54" s="67"/>
     </row>
@@ -14031,13 +14072,13 @@
       <c r="H55" s="106"/>
       <c r="I55" s="105"/>
       <c r="J55" s="106"/>
-      <c r="K55" s="109"/>
-      <c r="L55" s="110"/>
-      <c r="M55" s="110"/>
-      <c r="N55" s="110"/>
-      <c r="O55" s="110"/>
-      <c r="P55" s="110"/>
-      <c r="Q55" s="110"/>
+      <c r="K55" s="107"/>
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+      <c r="N55" s="108"/>
+      <c r="O55" s="108"/>
+      <c r="P55" s="108"/>
+      <c r="Q55" s="108"/>
       <c r="R55" s="114"/>
       <c r="S55" s="110"/>
       <c r="T55" s="110"/>
@@ -14059,14 +14100,14 @@
       <c r="H56" s="106"/>
       <c r="I56" s="105"/>
       <c r="J56" s="106"/>
-      <c r="K56" s="114"/>
+      <c r="K56" s="109"/>
       <c r="L56" s="110"/>
       <c r="M56" s="110"/>
       <c r="N56" s="110"/>
       <c r="O56" s="110"/>
       <c r="P56" s="110"/>
       <c r="Q56" s="133"/>
-      <c r="R56" s="114"/>
+      <c r="R56" s="109"/>
       <c r="S56" s="110"/>
       <c r="T56" s="110"/>
       <c r="U56" s="110"/>
@@ -14093,7 +14134,7 @@
       <c r="N57" s="110"/>
       <c r="O57" s="110"/>
       <c r="P57" s="110"/>
-      <c r="Q57" s="133"/>
+      <c r="Q57" s="110"/>
       <c r="R57" s="114"/>
       <c r="S57" s="110"/>
       <c r="T57" s="110"/>
@@ -14101,7 +14142,7 @@
       <c r="V57" s="110"/>
       <c r="W57" s="110"/>
       <c r="X57" s="110"/>
-      <c r="Y57" s="133"/>
+      <c r="Y57" s="110"/>
       <c r="Z57" s="67"/>
       <c r="AA57" s="67"/>
     </row>
@@ -14161,8 +14202,88 @@
       <c r="Z59" s="67"/>
       <c r="AA59" s="67"/>
     </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B60" s="103"/>
+      <c r="C60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="71"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="114"/>
+      <c r="L60" s="110"/>
+      <c r="M60" s="110"/>
+      <c r="N60" s="110"/>
+      <c r="O60" s="110"/>
+      <c r="P60" s="110"/>
+      <c r="Q60" s="133"/>
+      <c r="R60" s="114"/>
+      <c r="S60" s="110"/>
+      <c r="T60" s="110"/>
+      <c r="U60" s="110"/>
+      <c r="V60" s="110"/>
+      <c r="W60" s="110"/>
+      <c r="X60" s="110"/>
+      <c r="Y60" s="133"/>
+      <c r="Z60" s="67"/>
+      <c r="AA60" s="67"/>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B61" s="103"/>
+      <c r="C61" s="104"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="105"/>
+      <c r="H61" s="106"/>
+      <c r="I61" s="105"/>
+      <c r="J61" s="106"/>
+      <c r="K61" s="109"/>
+      <c r="L61" s="110"/>
+      <c r="M61" s="110"/>
+      <c r="N61" s="110"/>
+      <c r="O61" s="110"/>
+      <c r="P61" s="110"/>
+      <c r="Q61" s="133"/>
+      <c r="R61" s="114"/>
+      <c r="S61" s="110"/>
+      <c r="T61" s="110"/>
+      <c r="U61" s="110"/>
+      <c r="V61" s="110"/>
+      <c r="W61" s="110"/>
+      <c r="X61" s="110"/>
+      <c r="Y61" s="133"/>
+      <c r="Z61" s="67"/>
+      <c r="AA61" s="67"/>
+    </row>
   </sheetData>
-  <mergeCells count="326">
+  <mergeCells count="338">
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:Y28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="R29:Y29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="K61:Q61"/>
+    <mergeCell ref="R61:Y61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:Q60"/>
+    <mergeCell ref="R60:Y60"/>
+    <mergeCell ref="Z60:AA60"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="G59:H59"/>
     <mergeCell ref="I59:J59"/>
@@ -14187,18 +14308,14 @@
     <mergeCell ref="K56:Q56"/>
     <mergeCell ref="R56:Y56"/>
     <mergeCell ref="Z56:AA56"/>
+    <mergeCell ref="R54:Y54"/>
+    <mergeCell ref="Z54:AA54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="K55:Q55"/>
     <mergeCell ref="R55:Y55"/>
     <mergeCell ref="Z55:AA55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:Q54"/>
-    <mergeCell ref="R54:Y54"/>
-    <mergeCell ref="Z54:AA54"/>
     <mergeCell ref="R52:Y52"/>
     <mergeCell ref="Z52:AA52"/>
     <mergeCell ref="B53:E53"/>
@@ -14207,6 +14324,12 @@
     <mergeCell ref="K53:Q53"/>
     <mergeCell ref="R53:Y53"/>
     <mergeCell ref="Z53:AA53"/>
+    <mergeCell ref="K46:Q46"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:Q44"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="R50:Y50"/>
     <mergeCell ref="Z50:AA50"/>
     <mergeCell ref="B51:E51"/>
@@ -14215,12 +14338,6 @@
     <mergeCell ref="K51:Q51"/>
     <mergeCell ref="R51:Y51"/>
     <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="K44:Q44"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:Q42"/>
-    <mergeCell ref="B44:E44"/>
     <mergeCell ref="R48:Y48"/>
     <mergeCell ref="Z48:AA48"/>
     <mergeCell ref="B49:E49"/>
@@ -14229,6 +14346,12 @@
     <mergeCell ref="K49:Q49"/>
     <mergeCell ref="R49:Y49"/>
     <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:Q42"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:Q40"/>
     <mergeCell ref="R46:Y46"/>
     <mergeCell ref="Z46:AA46"/>
     <mergeCell ref="B47:E47"/>
@@ -14237,12 +14360,6 @@
     <mergeCell ref="K47:Q47"/>
     <mergeCell ref="R47:Y47"/>
     <mergeCell ref="Z47:AA47"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:Q40"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:Q38"/>
     <mergeCell ref="R44:Y44"/>
     <mergeCell ref="Z44:AA44"/>
     <mergeCell ref="B45:E45"/>
@@ -14251,6 +14368,14 @@
     <mergeCell ref="K45:Q45"/>
     <mergeCell ref="R45:Y45"/>
     <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:Q38"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:Q36"/>
     <mergeCell ref="R42:Y42"/>
     <mergeCell ref="Z42:AA42"/>
     <mergeCell ref="B43:E43"/>
@@ -14259,14 +14384,6 @@
     <mergeCell ref="K43:Q43"/>
     <mergeCell ref="R43:Y43"/>
     <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:Q36"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:Q34"/>
     <mergeCell ref="R40:Y40"/>
     <mergeCell ref="Z40:AA40"/>
     <mergeCell ref="B41:E41"/>
@@ -14275,6 +14392,14 @@
     <mergeCell ref="K41:Q41"/>
     <mergeCell ref="R41:Y41"/>
     <mergeCell ref="Z41:AA41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:Q34"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:Q32"/>
     <mergeCell ref="R38:Y38"/>
     <mergeCell ref="Z38:AA38"/>
     <mergeCell ref="B39:E39"/>
@@ -14283,14 +14408,6 @@
     <mergeCell ref="K39:Q39"/>
     <mergeCell ref="R39:Y39"/>
     <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:Q30"/>
     <mergeCell ref="R36:Y36"/>
     <mergeCell ref="Z36:AA36"/>
     <mergeCell ref="B37:E37"/>
@@ -14299,6 +14416,14 @@
     <mergeCell ref="K37:Q37"/>
     <mergeCell ref="R37:Y37"/>
     <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:Q26"/>
     <mergeCell ref="R34:Y34"/>
     <mergeCell ref="Z34:AA34"/>
     <mergeCell ref="B35:E35"/>
@@ -14307,14 +14432,6 @@
     <mergeCell ref="K35:Q35"/>
     <mergeCell ref="R35:Y35"/>
     <mergeCell ref="Z35:AA35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:Q26"/>
     <mergeCell ref="R32:Y32"/>
     <mergeCell ref="Z32:AA32"/>
     <mergeCell ref="B33:E33"/>
@@ -14323,6 +14440,14 @@
     <mergeCell ref="K33:Q33"/>
     <mergeCell ref="R33:Y33"/>
     <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:Q22"/>
     <mergeCell ref="R30:Y30"/>
     <mergeCell ref="Z30:AA30"/>
     <mergeCell ref="B31:E31"/>
@@ -14331,22 +14456,6 @@
     <mergeCell ref="K31:Q31"/>
     <mergeCell ref="R31:Y31"/>
     <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="R28:Y28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="R29:Y29"/>
-    <mergeCell ref="Z29:AA29"/>
     <mergeCell ref="R26:Y26"/>
     <mergeCell ref="Z26:AA26"/>
     <mergeCell ref="B27:E27"/>
@@ -14355,8 +14464,8 @@
     <mergeCell ref="K27:Q27"/>
     <mergeCell ref="R27:Y27"/>
     <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="K20:Q20"/>
     <mergeCell ref="B18:E18"/>
@@ -14473,6 +14582,10 @@
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="R7:Y7"/>
     <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:Q54"/>
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="G52:H52"/>
     <mergeCell ref="I52:J52"/>
@@ -14485,10 +14598,6 @@
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="I48:J48"/>
     <mergeCell ref="K48:Q48"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:Q46"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14499,13 +14608,13 @@
           <x14:formula1>
             <xm:f>'Data Validation'!$H$3:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F7:F59</xm:sqref>
+          <xm:sqref>F7:F61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{050290D3-B85B-4EA2-A977-D0F62C4F398F}">
           <x14:formula1>
             <xm:f>'Data Validation'!$B$3:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>Z7:AA59</xm:sqref>
+          <xm:sqref>Z7:AA61</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14601,12 +14710,12 @@
     </row>
     <row r="7" spans="3:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="140" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D7" s="141"/>
       <c r="E7" s="141"/>
       <c r="F7" s="74" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G7" s="69"/>
       <c r="H7" s="69"/>
@@ -14639,7 +14748,7 @@
       <c r="D8" s="141"/>
       <c r="E8" s="141"/>
       <c r="F8" s="74" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="69"/>
@@ -14667,12 +14776,12 @@
     </row>
     <row r="9" spans="3:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" s="141"/>
       <c r="E9" s="141"/>
       <c r="F9" s="74" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G9" s="69"/>
       <c r="H9" s="69"/>
@@ -14705,7 +14814,7 @@
       <c r="D10" s="141"/>
       <c r="E10" s="141"/>
       <c r="F10" s="74" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G10" s="69"/>
       <c r="H10" s="69"/>
@@ -14721,7 +14830,7 @@
       </c>
       <c r="O10" s="67"/>
       <c r="P10" s="67" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q10" s="67"/>
       <c r="R10" s="67" t="s">
@@ -14731,12 +14840,12 @@
     </row>
     <row r="11" spans="3:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="140" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" s="141"/>
       <c r="E11" s="141"/>
       <c r="F11" s="74" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G11" s="69"/>
       <c r="H11" s="69"/>
@@ -14762,12 +14871,12 @@
     </row>
     <row r="12" spans="3:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="140" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D12" s="141"/>
       <c r="E12" s="141"/>
       <c r="F12" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G12" s="69"/>
       <c r="H12" s="69"/>
@@ -14798,7 +14907,7 @@
       <c r="D13" s="141"/>
       <c r="E13" s="141"/>
       <c r="F13" s="74" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69"/>
@@ -14824,12 +14933,12 @@
     </row>
     <row r="14" spans="3:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="140" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" s="141"/>
       <c r="E14" s="141"/>
       <c r="F14" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G14" s="69"/>
       <c r="H14" s="69"/>
@@ -14860,7 +14969,7 @@
       <c r="D15" s="139"/>
       <c r="E15" s="139"/>
       <c r="F15" s="74" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G15" s="69"/>
       <c r="H15" s="69"/>
@@ -16067,7 +16176,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{11DDDF4D-8407-4BB3-A079-C5BCA91EBEE6}">
           <x14:formula1>
             <xm:f>'Data Validation'!$F$3:$F$5</xm:f>
@@ -16209,7 +16318,7 @@
       </c>
       <c r="C11" s="142"/>
       <c r="D11" s="83" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -16269,7 +16378,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
@@ -16295,7 +16404,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
@@ -16308,7 +16417,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -16411,7 +16520,7 @@
     <row r="2" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -16451,11 +16560,11 @@
     </row>
     <row r="7" spans="2:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="150"/>
       <c r="D7" s="83" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -16467,18 +16576,18 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
@@ -16498,19 +16607,19 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="E14" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="E15" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="E16" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J16" s="7"/>
     </row>
@@ -16524,22 +16633,22 @@
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E19" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D24" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
@@ -16566,7 +16675,7 @@
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E27" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F27" s="30"/>
       <c r="G27" s="30"/>
@@ -16578,7 +16687,7 @@
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E28" s="34" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F28" s="30"/>
       <c r="G28" s="30"/>
@@ -16600,7 +16709,7 @@
     </row>
     <row r="31" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D31" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.25">
@@ -16618,19 +16727,19 @@
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E34" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E35" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E36" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I36" s="7"/>
     </row>
@@ -16643,22 +16752,22 @@
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D42" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E43" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F43" s="156"/>
       <c r="G43" s="4"/>
@@ -16672,7 +16781,7 @@
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E44" s="6"/>
       <c r="F44" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G44" s="24"/>
       <c r="M44" s="7"/>
@@ -16680,49 +16789,49 @@
     <row r="45" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E45" s="6"/>
       <c r="G45" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M45" s="7"/>
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E46" s="6"/>
       <c r="G46" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M46" s="7"/>
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E47" s="6"/>
       <c r="G47" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M47" s="7"/>
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E48" s="6"/>
       <c r="G48" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E49" s="6"/>
       <c r="G49" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M49" s="7"/>
     </row>
     <row r="50" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E50" s="6"/>
       <c r="G50" s="24" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M50" s="7"/>
     </row>
     <row r="51" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E51" s="6"/>
       <c r="F51" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G51" s="24"/>
       <c r="M51" s="7"/>
@@ -16730,14 +16839,14 @@
     <row r="52" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E52" s="6"/>
       <c r="G52" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M52" s="7"/>
     </row>
     <row r="53" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E53" s="6"/>
       <c r="F53" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G53" s="24"/>
       <c r="M53" s="7"/>
@@ -16745,7 +16854,7 @@
     <row r="54" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E54" s="6"/>
       <c r="G54" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M54" s="7"/>
     </row>
@@ -16762,7 +16871,7 @@
     </row>
     <row r="57" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E57" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="5:15" x14ac:dyDescent="0.25">
@@ -16777,7 +16886,7 @@
       <c r="L58" s="37"/>
       <c r="M58" s="38"/>
       <c r="O58" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="5:15" x14ac:dyDescent="0.25">
@@ -16792,7 +16901,7 @@
     </row>
     <row r="60" spans="5:15" x14ac:dyDescent="0.25">
       <c r="F60" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G60" s="39"/>
       <c r="H60" s="39"/>
@@ -16804,7 +16913,7 @@
     </row>
     <row r="61" spans="5:15" x14ac:dyDescent="0.25">
       <c r="F61" s="43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G61" s="39"/>
       <c r="H61" s="39"/>
@@ -16816,7 +16925,7 @@
     </row>
     <row r="62" spans="5:15" x14ac:dyDescent="0.25">
       <c r="F62" s="43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G62" s="39"/>
       <c r="H62" s="39"/>
@@ -16838,7 +16947,7 @@
     </row>
     <row r="65" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D65" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="4:10" x14ac:dyDescent="0.25">
@@ -16859,7 +16968,7 @@
     </row>
     <row r="68" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E68" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F68" s="30"/>
       <c r="G68" s="30"/>
@@ -16868,7 +16977,7 @@
     </row>
     <row r="69" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E69" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F69" s="30"/>
       <c r="G69" s="30"/>
@@ -16877,7 +16986,7 @@
     </row>
     <row r="70" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E70" s="34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F70" s="30"/>
       <c r="G70" s="30"/>
@@ -16893,7 +17002,7 @@
     </row>
     <row r="73" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D73" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="4:10" x14ac:dyDescent="0.25">
@@ -16916,7 +17025,7 @@
     </row>
     <row r="76" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E76" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F76" s="30"/>
       <c r="G76" s="30"/>
@@ -16926,7 +17035,7 @@
     </row>
     <row r="77" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E77" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F77" s="30"/>
       <c r="G77" s="30"/>
@@ -16936,7 +17045,7 @@
     </row>
     <row r="78" spans="4:10" x14ac:dyDescent="0.25">
       <c r="E78" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F78" s="30"/>
       <c r="G78" s="30"/>
@@ -16954,17 +17063,17 @@
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D81" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" spans="2:12" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C84" s="150"/>
       <c r="D84" s="83" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E84" s="83"/>
       <c r="F84" s="83"/>
@@ -16979,22 +17088,22 @@
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="2:12" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D88" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E89" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F89" s="156"/>
       <c r="G89" s="4"/>
@@ -17007,7 +17116,7 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E90" s="6"/>
       <c r="F90" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G90" s="24"/>
       <c r="L90" s="7"/>
@@ -17015,49 +17124,49 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E91" s="6"/>
       <c r="G91" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L91" s="7"/>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E92" s="6"/>
       <c r="G92" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L92" s="7"/>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E93" s="6"/>
       <c r="G93" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L93" s="7"/>
     </row>
     <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E94" s="6"/>
       <c r="G94" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L94" s="7"/>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E95" s="6"/>
       <c r="G95" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L95" s="7"/>
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E96" s="6"/>
       <c r="G96" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L96" s="7"/>
     </row>
     <row r="97" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E97" s="6"/>
       <c r="F97" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G97" s="24"/>
       <c r="L97" s="7"/>
@@ -17065,14 +17174,14 @@
     <row r="98" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E98" s="6"/>
       <c r="G98" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L98" s="7"/>
     </row>
     <row r="99" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E99" s="6"/>
       <c r="F99" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G99" s="24"/>
       <c r="L99" s="7"/>
@@ -17080,7 +17189,7 @@
     <row r="100" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E100" s="6"/>
       <c r="G100" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L100" s="7"/>
     </row>
@@ -17096,7 +17205,7 @@
     </row>
     <row r="103" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="4:15" x14ac:dyDescent="0.25">
@@ -17111,7 +17220,7 @@
       <c r="L104" s="37"/>
       <c r="M104" s="38"/>
       <c r="O104" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="4:15" x14ac:dyDescent="0.25">
@@ -17126,7 +17235,7 @@
     </row>
     <row r="106" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F106" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G106" s="39"/>
       <c r="H106" s="39"/>
@@ -17138,7 +17247,7 @@
     </row>
     <row r="107" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F107" s="43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G107" s="39"/>
       <c r="H107" s="39"/>
@@ -17150,7 +17259,7 @@
     </row>
     <row r="108" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F108" s="43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G108" s="39"/>
       <c r="H108" s="39"/>
@@ -17172,7 +17281,7 @@
     </row>
     <row r="111" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D111" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="4:15" x14ac:dyDescent="0.25">
@@ -17184,7 +17293,7 @@
       <c r="H112" s="28"/>
       <c r="I112" s="29"/>
       <c r="K112" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="113" spans="4:12" x14ac:dyDescent="0.25">
@@ -17196,7 +17305,7 @@
     </row>
     <row r="114" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E114" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F114" s="30"/>
       <c r="G114" s="30"/>
@@ -17205,7 +17314,7 @@
     </row>
     <row r="115" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E115" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F115" s="30"/>
       <c r="G115" s="30"/>
@@ -17214,7 +17323,7 @@
     </row>
     <row r="116" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E116" s="34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F116" s="30"/>
       <c r="G116" s="30"/>
@@ -17230,7 +17339,7 @@
     </row>
     <row r="119" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D119" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="4:12" x14ac:dyDescent="0.25">
@@ -17243,7 +17352,7 @@
       <c r="I120" s="28"/>
       <c r="J120" s="29"/>
       <c r="L120" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" spans="4:12" x14ac:dyDescent="0.25">
@@ -17256,7 +17365,7 @@
     </row>
     <row r="122" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E122" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F122" s="30"/>
       <c r="G122" s="30"/>
@@ -17266,7 +17375,7 @@
     </row>
     <row r="123" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E123" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F123" s="30"/>
       <c r="G123" s="30"/>
@@ -17276,7 +17385,7 @@
     </row>
     <row r="124" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E124" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F124" s="30"/>
       <c r="G124" s="30"/>
@@ -17294,17 +17403,17 @@
     </row>
     <row r="127" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E127" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="129" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C129" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D130" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131" spans="3:11" x14ac:dyDescent="0.25">
@@ -17329,7 +17438,7 @@
     </row>
     <row r="133" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E133" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F133" s="30"/>
       <c r="G133" s="30"/>
@@ -17340,7 +17449,7 @@
     </row>
     <row r="134" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E134" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F134" s="30"/>
       <c r="G134" s="30"/>
@@ -17351,7 +17460,7 @@
     </row>
     <row r="135" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E135" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F135" s="30"/>
       <c r="G135" s="30"/>
@@ -17417,7 +17526,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -17461,7 +17570,7 @@
       </c>
       <c r="C7" s="159"/>
       <c r="D7" s="83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
@@ -17477,7 +17586,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -17509,7 +17618,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -17525,7 +17634,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -17541,7 +17650,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="160" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E12" s="160"/>
       <c r="F12" s="160"/>
@@ -17557,7 +17666,7 @@
       </c>
       <c r="C13" s="159"/>
       <c r="D13" s="160" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E13" s="160"/>
       <c r="F13" s="160"/>
@@ -17569,43 +17678,43 @@
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F26" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.25">
@@ -17624,19 +17733,19 @@
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G29" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G30" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L30" s="7"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G31" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -17650,68 +17759,68 @@
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E35" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="4:11" x14ac:dyDescent="0.25">
       <c r="F37" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E38" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E39" s="3"/>
       <c r="F39" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E40" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E41" s="3"/>
       <c r="F41" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E42" s="3"/>
       <c r="F42" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E43" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E44" s="3"/>
       <c r="F44" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E45" s="3"/>
       <c r="F45" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="4:11" x14ac:dyDescent="0.25">
@@ -17719,7 +17828,7 @@
     </row>
     <row r="47" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E47" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="4:11" x14ac:dyDescent="0.25">
@@ -17738,19 +17847,19 @@
     </row>
     <row r="50" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F50" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K50" s="7"/>
     </row>
     <row r="51" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F51" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K51" s="7"/>
     </row>
     <row r="52" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F52" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K52" s="7"/>
     </row>
@@ -17764,38 +17873,38 @@
     </row>
     <row r="56" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C56" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E58" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E59" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D61" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E62" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F63" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G63" s="47"/>
       <c r="H63" s="4"/>
@@ -17817,7 +17926,7 @@
     <row r="64" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F64" s="6"/>
       <c r="G64" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H64" s="24"/>
       <c r="V64" s="7"/>
@@ -17825,7 +17934,7 @@
     <row r="65" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F65" s="6"/>
       <c r="G65" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H65" s="24"/>
       <c r="V65" s="7"/>
@@ -17833,35 +17942,35 @@
     <row r="66" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F66" s="6"/>
       <c r="H66" s="24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="V66" s="7"/>
     </row>
     <row r="67" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F67" s="6"/>
       <c r="H67" s="24" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="V67" s="7"/>
     </row>
     <row r="68" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F68" s="6"/>
       <c r="H68" s="24" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F69" s="6"/>
       <c r="H69" s="24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="V69" s="7"/>
     </row>
     <row r="70" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F70" s="6"/>
       <c r="G70" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H70" s="24"/>
       <c r="V70" s="7"/>
@@ -17870,7 +17979,7 @@
       <c r="F71" s="6"/>
       <c r="G71" s="36"/>
       <c r="H71" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="V71" s="7"/>
     </row>
@@ -17895,7 +18004,7 @@
     </row>
     <row r="74" spans="6:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F74" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="6:22" x14ac:dyDescent="0.25">
@@ -17913,19 +18022,19 @@
     </row>
     <row r="77" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G77" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K77" s="7"/>
     </row>
     <row r="78" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G78" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K78" s="7"/>
     </row>
     <row r="79" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G79" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K79" s="7"/>
     </row>
@@ -17970,28 +18079,28 @@
     <row r="87" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K87" s="7"/>
     </row>
     <row r="88" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K88" s="7"/>
     </row>
     <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K89" s="7"/>
     </row>
     <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K90" s="7"/>
     </row>
@@ -18052,7 +18161,7 @@
     <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="85" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D3" s="86"/>
       <c r="E3" s="86"/>
@@ -18112,7 +18221,7 @@
       </c>
       <c r="C8" s="159"/>
       <c r="D8" s="83" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E8" s="83"/>
       <c r="F8" s="83"/>
@@ -18144,7 +18253,7 @@
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="83" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E10" s="83"/>
       <c r="F10" s="83"/>
@@ -18160,7 +18269,7 @@
       </c>
       <c r="C11" s="159"/>
       <c r="D11" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="83"/>
       <c r="F11" s="83"/>
@@ -18176,7 +18285,7 @@
       </c>
       <c r="C12" s="159"/>
       <c r="D12" s="160" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E12" s="160"/>
       <c r="F12" s="160"/>
@@ -18188,39 +18297,39 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="D16" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F21" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
@@ -18239,19 +18348,19 @@
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G24" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L24" s="7"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G25" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L25" s="7"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G26" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L26" s="7"/>
     </row>
@@ -18265,51 +18374,51 @@
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E30" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E31" s="3"/>
       <c r="F31" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F32" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E33" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E34" s="3"/>
       <c r="F34" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E35" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E37" s="3"/>
       <c r="F37" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
@@ -18317,7 +18426,7 @@
     </row>
     <row r="39" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E39" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.25">
@@ -18336,19 +18445,19 @@
     </row>
     <row r="42" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F42" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F43" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K43" s="7"/>
     </row>
     <row r="44" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K44" s="7"/>
     </row>
@@ -18362,44 +18471,44 @@
     </row>
     <row r="48" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C48" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C50" s="2"/>
       <c r="E50" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E51" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E52" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D54" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E55" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F56" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G56" s="47"/>
       <c r="H56" s="4"/>
@@ -18421,7 +18530,7 @@
     <row r="57" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F57" s="6"/>
       <c r="G57" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H57" s="24"/>
       <c r="V57" s="7"/>
@@ -18429,105 +18538,105 @@
     <row r="58" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F58" s="6"/>
       <c r="H58" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="V58" s="7"/>
     </row>
     <row r="59" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F59" s="6"/>
       <c r="H59" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="V59" s="7"/>
     </row>
     <row r="60" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F60" s="6"/>
       <c r="H60" s="24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V60" s="7"/>
     </row>
     <row r="61" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F61" s="6"/>
       <c r="H61" s="24" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="V61" s="7"/>
     </row>
     <row r="62" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F62" s="6"/>
       <c r="H62" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V62" s="7"/>
     </row>
     <row r="63" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F63" s="6"/>
       <c r="H63" s="24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V63" s="7"/>
     </row>
     <row r="64" spans="3:22" x14ac:dyDescent="0.25">
       <c r="F64" s="6"/>
       <c r="H64" s="24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V64" s="7"/>
     </row>
     <row r="65" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F65" s="6"/>
       <c r="H65" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="V65" s="7"/>
     </row>
     <row r="66" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F66" s="6"/>
       <c r="H66" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="V66" s="7"/>
     </row>
     <row r="67" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F67" s="6"/>
       <c r="H67" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="V67" s="7"/>
     </row>
     <row r="68" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F68" s="6"/>
       <c r="H68" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F69" s="6"/>
       <c r="H69" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="V69" s="7"/>
     </row>
     <row r="70" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F70" s="6"/>
       <c r="H70" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="V70" s="7"/>
     </row>
     <row r="71" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F71" s="6"/>
       <c r="H71" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V71" s="7"/>
     </row>
     <row r="72" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F72" s="6"/>
       <c r="G72" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H72" s="24"/>
       <c r="V72" s="7"/>
@@ -18535,7 +18644,7 @@
     <row r="73" spans="6:22" x14ac:dyDescent="0.25">
       <c r="F73" s="6"/>
       <c r="G73" s="36" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H73" s="24"/>
       <c r="V73" s="7"/>
@@ -18561,7 +18670,7 @@
     </row>
     <row r="76" spans="6:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F76" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="6:22" x14ac:dyDescent="0.25">
@@ -18579,19 +18688,19 @@
     </row>
     <row r="79" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G79" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K79" s="7"/>
     </row>
     <row r="80" spans="6:22" x14ac:dyDescent="0.25">
       <c r="G80" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K80" s="7"/>
     </row>
     <row r="81" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G81" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K81" s="7"/>
     </row>
@@ -18636,28 +18745,28 @@
     <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K89" s="7"/>
     </row>
     <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K90" s="7"/>
     </row>
     <row r="91" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K91" s="7"/>
     </row>
     <row r="92" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K92" s="7"/>
     </row>
